--- a/GestionAmbiental/wwwroot/ExcelTemplates/Incidentes/ReportePreliminar/JU-MAP-STD-001.F01_Reporte preliminar de incidente ambiental_V00.xlsx
+++ b/GestionAmbiental/wwwroot/ExcelTemplates/Incidentes/ReportePreliminar/JU-MAP-STD-001.F01_Reporte preliminar de incidente ambiental_V00.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electrodata\Marcobre\Tablas Maestras\Marcobre-GestionAmbiental\GestionAmbiental\wwwroot\ExcelTemplates\Incidentes\ReportePreliminar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6BBBB9-3173-4F56-A12A-4BB98E5DD44E}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D8EFF5-7342-4450-AFE9-FF1620F85366}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,9 +20,9 @@
     <externalReference r:id="rId3"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RPIA!$A$1:$AA$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RPIA!$A:$AA</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,164 +35,6 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Olivia Valencia</author>
-    <author>Carlos Gabriel Mego Armas</author>
-  </authors>
-  <commentList>
-    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>SGA:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-En caso el incidente no corresponda a un derrame, colocar tres guiones.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>SGA:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-En caso no corresponda a un derrame, colocar tres guiones.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>SGA:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Seleccione unidad de medida.
-En caso no corresponda a un derrame elegir N.A.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Y16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>SGA:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Seleccionar unidad de medida</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>SGA:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Ejem.:
-Tajo, Nivel 764</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W17" authorId="1" shapeId="0" xr:uid="{F128E3DD-5750-4476-9A30-B13CD66122D9}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>SGA:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Seleccionar
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Olivia Valencia</author>
@@ -3596,9 +3438,6 @@
     <t>Carlos Mego</t>
   </si>
   <si>
-    <t>CAUSAS DEL INCIDENTE</t>
-  </si>
-  <si>
     <t>Otra causa inmediata:</t>
   </si>
   <si>
@@ -3630,6 +3469,9 @@
   </si>
   <si>
     <t>Contratista</t>
+  </si>
+  <si>
+    <t>CAUSAS INMEDIATAS DEL INCIDENTE</t>
   </si>
 </sst>
 </file>
@@ -3639,7 +3481,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3708,13 +3550,6 @@
       <b/>
       <sz val="10"/>
       <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1" tint="0.499984740745262"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -3987,7 +3822,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4068,7 +3903,7 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4271,7 +4106,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4290,7 +4125,7 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -4303,7 +4138,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4349,7 +4184,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4381,10 +4216,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4506,6 +4337,33 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4515,36 +4373,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4558,12 +4386,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5081,11 +4903,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z53"/>
+  <dimension ref="A1:Z33"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1" style="9" customWidth="1"/>
@@ -5121,113 +4943,113 @@
     <row r="1" spans="1:26" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
-      <c r="B2" s="146"/>
-      <c r="C2" s="147" t="s">
+      <c r="B2" s="145"/>
+      <c r="C2" s="146" t="s">
         <v>439</v>
       </c>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
-      <c r="K2" s="147"/>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147"/>
-      <c r="P2" s="147"/>
-      <c r="Q2" s="147"/>
-      <c r="R2" s="147"/>
-      <c r="S2" s="147"/>
-      <c r="T2" s="147"/>
-      <c r="U2" s="147"/>
-      <c r="V2" s="147"/>
-      <c r="W2" s="147"/>
-      <c r="X2" s="152"/>
-      <c r="Y2" s="153"/>
-      <c r="Z2" s="154"/>
+      <c r="D2" s="146"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="146"/>
+      <c r="I2" s="146"/>
+      <c r="J2" s="146"/>
+      <c r="K2" s="146"/>
+      <c r="L2" s="146"/>
+      <c r="M2" s="146"/>
+      <c r="N2" s="146"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="146"/>
+      <c r="R2" s="146"/>
+      <c r="S2" s="146"/>
+      <c r="T2" s="146"/>
+      <c r="U2" s="146"/>
+      <c r="V2" s="146"/>
+      <c r="W2" s="146"/>
+      <c r="X2" s="151"/>
+      <c r="Y2" s="152"/>
+      <c r="Z2" s="153"/>
     </row>
     <row r="3" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
-      <c r="B3" s="146"/>
-      <c r="C3" s="161" t="s">
+      <c r="B3" s="145"/>
+      <c r="C3" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="162"/>
-      <c r="E3" s="163" t="s">
+      <c r="D3" s="161"/>
+      <c r="E3" s="162" t="s">
         <v>485</v>
       </c>
-      <c r="F3" s="163"/>
-      <c r="G3" s="163"/>
-      <c r="H3" s="163"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="163"/>
-      <c r="K3" s="164"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="162"/>
+      <c r="H3" s="162"/>
+      <c r="I3" s="162"/>
+      <c r="J3" s="162"/>
+      <c r="K3" s="163"/>
       <c r="L3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="M3" s="5"/>
-      <c r="N3" s="170">
+      <c r="N3" s="169">
         <v>43831</v>
       </c>
-      <c r="O3" s="168"/>
-      <c r="P3" s="169"/>
+      <c r="O3" s="167"/>
+      <c r="P3" s="168"/>
       <c r="Q3" s="4" t="s">
         <v>18</v>
       </c>
       <c r="R3" s="98"/>
-      <c r="S3" s="150">
+      <c r="S3" s="149">
         <v>0</v>
       </c>
-      <c r="T3" s="150"/>
-      <c r="U3" s="150"/>
-      <c r="V3" s="150"/>
-      <c r="W3" s="151"/>
-      <c r="X3" s="155"/>
-      <c r="Y3" s="156"/>
-      <c r="Z3" s="157"/>
+      <c r="T3" s="149"/>
+      <c r="U3" s="149"/>
+      <c r="V3" s="149"/>
+      <c r="W3" s="150"/>
+      <c r="X3" s="154"/>
+      <c r="Y3" s="155"/>
+      <c r="Z3" s="156"/>
     </row>
     <row r="4" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
-      <c r="B4" s="146"/>
+      <c r="B4" s="145"/>
       <c r="C4" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="165" t="s">
+      <c r="D4" s="164" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="165"/>
-      <c r="F4" s="165"/>
-      <c r="G4" s="165"/>
-      <c r="H4" s="165"/>
-      <c r="I4" s="165"/>
-      <c r="J4" s="165"/>
-      <c r="K4" s="166"/>
-      <c r="L4" s="167" t="s">
+      <c r="E4" s="164"/>
+      <c r="F4" s="164"/>
+      <c r="G4" s="164"/>
+      <c r="H4" s="164"/>
+      <c r="I4" s="164"/>
+      <c r="J4" s="164"/>
+      <c r="K4" s="165"/>
+      <c r="L4" s="166" t="s">
         <v>0</v>
       </c>
-      <c r="M4" s="150"/>
-      <c r="N4" s="168">
+      <c r="M4" s="149"/>
+      <c r="N4" s="167">
         <v>1</v>
       </c>
-      <c r="O4" s="168"/>
-      <c r="P4" s="169"/>
-      <c r="Q4" s="174" t="s">
+      <c r="O4" s="167"/>
+      <c r="P4" s="168"/>
+      <c r="Q4" s="173" t="s">
         <v>20</v>
       </c>
-      <c r="R4" s="175"/>
-      <c r="S4" s="175"/>
-      <c r="T4" s="175"/>
-      <c r="U4" s="175"/>
-      <c r="V4" s="176">
+      <c r="R4" s="174"/>
+      <c r="S4" s="174"/>
+      <c r="T4" s="174"/>
+      <c r="U4" s="174"/>
+      <c r="V4" s="175">
         <v>43818</v>
       </c>
-      <c r="W4" s="144"/>
-      <c r="X4" s="158"/>
-      <c r="Y4" s="159"/>
-      <c r="Z4" s="160"/>
+      <c r="W4" s="143"/>
+      <c r="X4" s="157"/>
+      <c r="Y4" s="158"/>
+      <c r="Z4" s="159"/>
     </row>
     <row r="5" spans="1:26" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
@@ -5258,89 +5080,89 @@
       <c r="Z5" s="54"/>
     </row>
     <row r="6" spans="1:26" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="149" t="s">
+      <c r="B6" s="148" t="s">
         <v>419</v>
       </c>
-      <c r="C6" s="149"/>
-      <c r="D6" s="149"/>
-      <c r="E6" s="149"/>
-      <c r="F6" s="149"/>
-      <c r="G6" s="149"/>
-      <c r="H6" s="149"/>
-      <c r="I6" s="149"/>
-      <c r="J6" s="149"/>
-      <c r="K6" s="149"/>
-      <c r="L6" s="149"/>
-      <c r="M6" s="149"/>
-      <c r="N6" s="149"/>
-      <c r="O6" s="149"/>
-      <c r="P6" s="149"/>
-      <c r="Q6" s="149"/>
-      <c r="R6" s="149"/>
-      <c r="S6" s="149"/>
-      <c r="T6" s="149"/>
-      <c r="U6" s="149"/>
-      <c r="V6" s="149"/>
-      <c r="W6" s="149"/>
-      <c r="X6" s="149"/>
-      <c r="Y6" s="149"/>
-      <c r="Z6" s="149"/>
+      <c r="C6" s="148"/>
+      <c r="D6" s="148"/>
+      <c r="E6" s="148"/>
+      <c r="F6" s="148"/>
+      <c r="G6" s="148"/>
+      <c r="H6" s="148"/>
+      <c r="I6" s="148"/>
+      <c r="J6" s="148"/>
+      <c r="K6" s="148"/>
+      <c r="L6" s="148"/>
+      <c r="M6" s="148"/>
+      <c r="N6" s="148"/>
+      <c r="O6" s="148"/>
+      <c r="P6" s="148"/>
+      <c r="Q6" s="148"/>
+      <c r="R6" s="148"/>
+      <c r="S6" s="148"/>
+      <c r="T6" s="148"/>
+      <c r="U6" s="148"/>
+      <c r="V6" s="148"/>
+      <c r="W6" s="148"/>
+      <c r="X6" s="148"/>
+      <c r="Y6" s="148"/>
+      <c r="Z6" s="148"/>
     </row>
     <row r="7" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="109" t="s">
         <v>412</v>
       </c>
-      <c r="C7" s="172" t="s">
+      <c r="C7" s="171" t="s">
         <v>487</v>
       </c>
-      <c r="D7" s="172"/>
-      <c r="E7" s="172"/>
-      <c r="F7" s="172"/>
-      <c r="G7" s="172"/>
-      <c r="H7" s="172"/>
-      <c r="I7" s="172"/>
-      <c r="J7" s="172"/>
-      <c r="K7" s="172"/>
-      <c r="L7" s="172"/>
+      <c r="D7" s="171"/>
+      <c r="E7" s="171"/>
+      <c r="F7" s="171"/>
+      <c r="G7" s="171"/>
+      <c r="H7" s="171"/>
+      <c r="I7" s="171"/>
+      <c r="J7" s="171"/>
+      <c r="K7" s="171"/>
+      <c r="L7" s="171"/>
       <c r="M7" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="N7" s="173">
+      <c r="N7" s="172">
         <v>20508972734</v>
       </c>
-      <c r="O7" s="173"/>
-      <c r="P7" s="173"/>
-      <c r="Q7" s="173"/>
-      <c r="R7" s="173"/>
-      <c r="S7" s="171" t="s">
+      <c r="O7" s="172"/>
+      <c r="P7" s="172"/>
+      <c r="Q7" s="172"/>
+      <c r="R7" s="172"/>
+      <c r="S7" s="170" t="s">
         <v>416</v>
       </c>
-      <c r="T7" s="171"/>
-      <c r="U7" s="171"/>
-      <c r="V7" s="171"/>
-      <c r="W7" s="148" t="s">
+      <c r="T7" s="170"/>
+      <c r="U7" s="170"/>
+      <c r="V7" s="170"/>
+      <c r="W7" s="147" t="s">
         <v>490</v>
       </c>
-      <c r="X7" s="143"/>
-      <c r="Y7" s="143"/>
-      <c r="Z7" s="144"/>
+      <c r="X7" s="142"/>
+      <c r="Y7" s="142"/>
+      <c r="Z7" s="143"/>
     </row>
     <row r="8" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="51" t="s">
         <v>414</v>
       </c>
-      <c r="C8" s="174" t="s">
+      <c r="C8" s="173" t="s">
         <v>488</v>
       </c>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
-      <c r="G8" s="175"/>
-      <c r="H8" s="175"/>
-      <c r="I8" s="175"/>
-      <c r="J8" s="175"/>
-      <c r="K8" s="175"/>
-      <c r="L8" s="187"/>
+      <c r="D8" s="174"/>
+      <c r="E8" s="174"/>
+      <c r="F8" s="174"/>
+      <c r="G8" s="174"/>
+      <c r="H8" s="174"/>
+      <c r="I8" s="174"/>
+      <c r="J8" s="174"/>
+      <c r="K8" s="174"/>
+      <c r="L8" s="182"/>
       <c r="M8" s="105" t="s">
         <v>415</v>
       </c>
@@ -5351,16 +5173,16 @@
       <c r="P8" s="126"/>
       <c r="Q8" s="126"/>
       <c r="R8" s="126"/>
-      <c r="S8" s="177" t="s">
+      <c r="S8" s="176" t="s">
         <v>489</v>
       </c>
-      <c r="T8" s="177"/>
-      <c r="U8" s="177"/>
-      <c r="V8" s="177"/>
-      <c r="W8" s="188"/>
-      <c r="X8" s="189"/>
-      <c r="Y8" s="189"/>
-      <c r="Z8" s="190"/>
+      <c r="T8" s="176"/>
+      <c r="U8" s="176"/>
+      <c r="V8" s="176"/>
+      <c r="W8" s="183"/>
+      <c r="X8" s="184"/>
+      <c r="Y8" s="184"/>
+      <c r="Z8" s="185"/>
     </row>
     <row r="9" spans="1:26" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
@@ -5391,33 +5213,33 @@
       <c r="Z9" s="84"/>
     </row>
     <row r="10" spans="1:26" ht="23.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="149" t="s">
+      <c r="B10" s="148" t="s">
         <v>491</v>
       </c>
-      <c r="C10" s="149"/>
-      <c r="D10" s="149"/>
-      <c r="E10" s="149"/>
-      <c r="F10" s="149"/>
-      <c r="G10" s="149"/>
-      <c r="H10" s="149"/>
-      <c r="I10" s="149"/>
-      <c r="J10" s="149"/>
-      <c r="K10" s="149"/>
-      <c r="L10" s="149"/>
-      <c r="M10" s="149"/>
-      <c r="N10" s="149"/>
-      <c r="O10" s="149"/>
-      <c r="P10" s="149"/>
-      <c r="Q10" s="149"/>
-      <c r="R10" s="149"/>
-      <c r="S10" s="149"/>
-      <c r="T10" s="149"/>
-      <c r="U10" s="149"/>
-      <c r="V10" s="149"/>
-      <c r="W10" s="149"/>
-      <c r="X10" s="149"/>
-      <c r="Y10" s="149"/>
-      <c r="Z10" s="149"/>
+      <c r="C10" s="148"/>
+      <c r="D10" s="148"/>
+      <c r="E10" s="148"/>
+      <c r="F10" s="148"/>
+      <c r="G10" s="148"/>
+      <c r="H10" s="148"/>
+      <c r="I10" s="148"/>
+      <c r="J10" s="148"/>
+      <c r="K10" s="148"/>
+      <c r="L10" s="148"/>
+      <c r="M10" s="148"/>
+      <c r="N10" s="148"/>
+      <c r="O10" s="148"/>
+      <c r="P10" s="148"/>
+      <c r="Q10" s="148"/>
+      <c r="R10" s="148"/>
+      <c r="S10" s="148"/>
+      <c r="T10" s="148"/>
+      <c r="U10" s="148"/>
+      <c r="V10" s="148"/>
+      <c r="W10" s="148"/>
+      <c r="X10" s="148"/>
+      <c r="Y10" s="148"/>
+      <c r="Z10" s="148"/>
     </row>
     <row r="11" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="109" t="s">
@@ -5436,52 +5258,52 @@
       <c r="M11" s="59" t="s">
         <v>413</v>
       </c>
-      <c r="N11" s="173"/>
-      <c r="O11" s="173"/>
-      <c r="P11" s="173"/>
-      <c r="Q11" s="173"/>
-      <c r="R11" s="173"/>
-      <c r="S11" s="171" t="s">
+      <c r="N11" s="172"/>
+      <c r="O11" s="172"/>
+      <c r="P11" s="172"/>
+      <c r="Q11" s="172"/>
+      <c r="R11" s="172"/>
+      <c r="S11" s="170" t="s">
         <v>416</v>
       </c>
-      <c r="T11" s="171"/>
-      <c r="U11" s="171"/>
-      <c r="V11" s="171"/>
-      <c r="W11" s="148"/>
-      <c r="X11" s="143"/>
-      <c r="Y11" s="143"/>
-      <c r="Z11" s="144"/>
+      <c r="T11" s="170"/>
+      <c r="U11" s="170"/>
+      <c r="V11" s="170"/>
+      <c r="W11" s="147"/>
+      <c r="X11" s="142"/>
+      <c r="Y11" s="142"/>
+      <c r="Z11" s="143"/>
     </row>
     <row r="12" spans="1:26" ht="26.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="51" t="s">
         <v>414</v>
       </c>
-      <c r="C12" s="148"/>
-      <c r="D12" s="143"/>
-      <c r="E12" s="143"/>
-      <c r="F12" s="143"/>
-      <c r="G12" s="143"/>
-      <c r="H12" s="143"/>
-      <c r="I12" s="143"/>
-      <c r="J12" s="143"/>
-      <c r="K12" s="143"/>
-      <c r="L12" s="143"/>
-      <c r="M12" s="143"/>
-      <c r="N12" s="143"/>
-      <c r="O12" s="143"/>
-      <c r="P12" s="143"/>
-      <c r="Q12" s="143"/>
-      <c r="R12" s="144"/>
-      <c r="S12" s="177" t="s">
+      <c r="C12" s="147"/>
+      <c r="D12" s="142"/>
+      <c r="E12" s="142"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="142"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="142"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="142"/>
+      <c r="L12" s="142"/>
+      <c r="M12" s="142"/>
+      <c r="N12" s="142"/>
+      <c r="O12" s="142"/>
+      <c r="P12" s="142"/>
+      <c r="Q12" s="142"/>
+      <c r="R12" s="143"/>
+      <c r="S12" s="176" t="s">
         <v>489</v>
       </c>
-      <c r="T12" s="177"/>
-      <c r="U12" s="177"/>
-      <c r="V12" s="177"/>
-      <c r="W12" s="188"/>
-      <c r="X12" s="189"/>
-      <c r="Y12" s="189"/>
-      <c r="Z12" s="190"/>
+      <c r="T12" s="176"/>
+      <c r="U12" s="176"/>
+      <c r="V12" s="176"/>
+      <c r="W12" s="183"/>
+      <c r="X12" s="184"/>
+      <c r="Y12" s="184"/>
+      <c r="Z12" s="185"/>
     </row>
     <row r="13" spans="1:26" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="99"/>
@@ -5544,23 +5366,23 @@
       <c r="B15" s="50" t="s">
         <v>417</v>
       </c>
-      <c r="C15" s="148"/>
-      <c r="D15" s="143"/>
-      <c r="E15" s="143"/>
-      <c r="F15" s="143"/>
-      <c r="G15" s="143"/>
-      <c r="H15" s="143"/>
-      <c r="I15" s="143"/>
-      <c r="J15" s="143"/>
-      <c r="K15" s="143"/>
-      <c r="L15" s="144"/>
+      <c r="C15" s="147"/>
+      <c r="D15" s="142"/>
+      <c r="E15" s="142"/>
+      <c r="F15" s="142"/>
+      <c r="G15" s="142"/>
+      <c r="H15" s="142"/>
+      <c r="I15" s="142"/>
+      <c r="J15" s="142"/>
+      <c r="K15" s="142"/>
+      <c r="L15" s="143"/>
       <c r="M15" s="114" t="s">
         <v>418</v>
       </c>
       <c r="N15" s="115"/>
-      <c r="O15" s="148"/>
-      <c r="P15" s="143"/>
-      <c r="Q15" s="144"/>
+      <c r="O15" s="147"/>
+      <c r="P15" s="142"/>
+      <c r="Q15" s="143"/>
       <c r="R15" s="132" t="s">
         <v>484</v>
       </c>
@@ -5580,16 +5402,16 @@
       <c r="B16" s="57" t="s">
         <v>427</v>
       </c>
-      <c r="C16" s="196"/>
-      <c r="D16" s="196"/>
-      <c r="E16" s="196"/>
-      <c r="F16" s="196"/>
-      <c r="G16" s="196"/>
-      <c r="H16" s="196"/>
-      <c r="I16" s="196"/>
-      <c r="J16" s="196"/>
-      <c r="K16" s="196"/>
-      <c r="L16" s="196"/>
+      <c r="C16" s="127"/>
+      <c r="D16" s="127"/>
+      <c r="E16" s="127"/>
+      <c r="F16" s="127"/>
+      <c r="G16" s="127"/>
+      <c r="H16" s="127"/>
+      <c r="I16" s="127"/>
+      <c r="J16" s="127"/>
+      <c r="K16" s="127"/>
+      <c r="L16" s="127"/>
       <c r="M16" s="128" t="s">
         <v>420</v>
       </c>
@@ -5613,30 +5435,30 @@
       <c r="B17" s="51" t="s">
         <v>421</v>
       </c>
-      <c r="C17" s="197"/>
-      <c r="D17" s="197"/>
-      <c r="E17" s="197"/>
-      <c r="F17" s="197"/>
-      <c r="G17" s="197"/>
-      <c r="H17" s="197"/>
-      <c r="I17" s="197"/>
-      <c r="J17" s="197"/>
-      <c r="K17" s="197"/>
-      <c r="L17" s="197"/>
+      <c r="C17" s="181"/>
+      <c r="D17" s="181"/>
+      <c r="E17" s="181"/>
+      <c r="F17" s="181"/>
+      <c r="G17" s="181"/>
+      <c r="H17" s="181"/>
+      <c r="I17" s="181"/>
+      <c r="J17" s="181"/>
+      <c r="K17" s="181"/>
+      <c r="L17" s="181"/>
       <c r="M17" s="128" t="s">
         <v>495</v>
       </c>
-      <c r="N17" s="184"/>
+      <c r="N17" s="180"/>
       <c r="O17" s="127"/>
       <c r="P17" s="127"/>
       <c r="Q17" s="127"/>
-      <c r="R17" s="181" t="s">
+      <c r="R17" s="177" t="s">
         <v>493</v>
       </c>
-      <c r="S17" s="182"/>
-      <c r="T17" s="182"/>
-      <c r="U17" s="182"/>
-      <c r="V17" s="183"/>
+      <c r="S17" s="178"/>
+      <c r="T17" s="178"/>
+      <c r="U17" s="178"/>
+      <c r="V17" s="179"/>
       <c r="W17" s="135"/>
       <c r="X17" s="136"/>
       <c r="Y17" s="136"/>
@@ -5644,38 +5466,38 @@
     </row>
     <row r="18" spans="1:26" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
-      <c r="B18" s="178" t="s">
+      <c r="B18" s="186" t="s">
         <v>428</v>
       </c>
-      <c r="C18" s="179"/>
-      <c r="D18" s="179"/>
-      <c r="E18" s="180"/>
-      <c r="F18" s="185"/>
-      <c r="G18" s="185"/>
-      <c r="H18" s="185"/>
-      <c r="I18" s="185"/>
-      <c r="J18" s="185"/>
-      <c r="K18" s="185"/>
-      <c r="L18" s="185"/>
-      <c r="M18" s="185"/>
-      <c r="N18" s="185"/>
-      <c r="O18" s="185"/>
-      <c r="P18" s="185"/>
-      <c r="Q18" s="185"/>
-      <c r="R18" s="185"/>
-      <c r="S18" s="185"/>
-      <c r="T18" s="185"/>
-      <c r="U18" s="185"/>
-      <c r="V18" s="185"/>
-      <c r="W18" s="185"/>
-      <c r="X18" s="185"/>
-      <c r="Y18" s="185"/>
-      <c r="Z18" s="186"/>
+      <c r="C18" s="187"/>
+      <c r="D18" s="187"/>
+      <c r="E18" s="188"/>
+      <c r="F18" s="142"/>
+      <c r="G18" s="142"/>
+      <c r="H18" s="142"/>
+      <c r="I18" s="142"/>
+      <c r="J18" s="142"/>
+      <c r="K18" s="142"/>
+      <c r="L18" s="142"/>
+      <c r="M18" s="142"/>
+      <c r="N18" s="142"/>
+      <c r="O18" s="142"/>
+      <c r="P18" s="142"/>
+      <c r="Q18" s="142"/>
+      <c r="R18" s="142"/>
+      <c r="S18" s="142"/>
+      <c r="T18" s="142"/>
+      <c r="U18" s="142"/>
+      <c r="V18" s="142"/>
+      <c r="W18" s="142"/>
+      <c r="X18" s="142"/>
+      <c r="Y18" s="142"/>
+      <c r="Z18" s="143"/>
     </row>
     <row r="19" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="124" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="C19" s="124"/>
       <c r="D19" s="124"/>
@@ -5705,13 +5527,13 @@
     <row r="20" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="118" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C20" s="119"/>
       <c r="D20" s="119"/>
       <c r="E20" s="120"/>
       <c r="F20" s="130" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G20" s="130"/>
       <c r="H20" s="130"/>
@@ -5723,7 +5545,7 @@
       <c r="N20" s="130"/>
       <c r="O20" s="130"/>
       <c r="P20" s="130" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="Q20" s="130"/>
       <c r="R20" s="130"/>
@@ -5739,7 +5561,7 @@
     <row r="21" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="132" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C21" s="133"/>
       <c r="D21" s="133"/>
@@ -5799,13 +5621,13 @@
     <row r="23" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="125" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C23" s="125"/>
       <c r="D23" s="125"/>
       <c r="E23" s="125"/>
       <c r="F23" s="125" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G23" s="125"/>
       <c r="H23" s="125"/>
@@ -5814,24 +5636,24 @@
       <c r="K23" s="125"/>
       <c r="L23" s="125"/>
       <c r="M23" s="131" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="N23" s="131"/>
       <c r="O23" s="131"/>
       <c r="P23" s="131" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="Q23" s="131"/>
       <c r="R23" s="131"/>
       <c r="S23" s="131"/>
       <c r="T23" s="131"/>
       <c r="U23" s="131" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="V23" s="131"/>
       <c r="W23" s="131"/>
       <c r="X23" s="131" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Y23" s="131"/>
       <c r="Z23" s="131"/>
@@ -5874,66 +5696,66 @@
       <c r="C25" s="121"/>
       <c r="D25" s="121"/>
       <c r="E25" s="122"/>
-      <c r="F25" s="139" t="s">
+      <c r="F25" s="138" t="s">
         <v>9</v>
       </c>
-      <c r="G25" s="140"/>
-      <c r="H25" s="140"/>
-      <c r="I25" s="140"/>
-      <c r="J25" s="140"/>
-      <c r="K25" s="140"/>
-      <c r="L25" s="140"/>
-      <c r="M25" s="140"/>
-      <c r="N25" s="140"/>
-      <c r="O25" s="141"/>
-      <c r="P25" s="139" t="s">
+      <c r="G25" s="139"/>
+      <c r="H25" s="139"/>
+      <c r="I25" s="139"/>
+      <c r="J25" s="139"/>
+      <c r="K25" s="139"/>
+      <c r="L25" s="139"/>
+      <c r="M25" s="139"/>
+      <c r="N25" s="139"/>
+      <c r="O25" s="140"/>
+      <c r="P25" s="138" t="s">
         <v>10</v>
       </c>
-      <c r="Q25" s="140"/>
-      <c r="R25" s="140"/>
-      <c r="S25" s="140"/>
-      <c r="T25" s="141"/>
-      <c r="U25" s="139" t="s">
-        <v>520</v>
-      </c>
-      <c r="V25" s="140"/>
-      <c r="W25" s="141"/>
+      <c r="Q25" s="139"/>
+      <c r="R25" s="139"/>
+      <c r="S25" s="139"/>
+      <c r="T25" s="140"/>
+      <c r="U25" s="138" t="s">
+        <v>519</v>
+      </c>
+      <c r="V25" s="139"/>
+      <c r="W25" s="140"/>
       <c r="X25" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="Y25" s="139" t="s">
+      <c r="Y25" s="138" t="s">
         <v>12</v>
       </c>
-      <c r="Z25" s="141"/>
+      <c r="Z25" s="140"/>
     </row>
     <row r="26" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="142" t="s">
+      <c r="B26" s="141" t="s">
         <v>430</v>
       </c>
-      <c r="C26" s="142"/>
-      <c r="D26" s="142"/>
-      <c r="E26" s="142"/>
-      <c r="F26" s="143"/>
-      <c r="G26" s="143"/>
-      <c r="H26" s="143"/>
-      <c r="I26" s="143"/>
-      <c r="J26" s="143"/>
-      <c r="K26" s="143"/>
-      <c r="L26" s="143"/>
-      <c r="M26" s="143"/>
-      <c r="N26" s="143"/>
-      <c r="O26" s="143"/>
-      <c r="P26" s="143"/>
-      <c r="Q26" s="143"/>
-      <c r="R26" s="143"/>
-      <c r="S26" s="143"/>
-      <c r="T26" s="143"/>
-      <c r="U26" s="143"/>
-      <c r="V26" s="143"/>
-      <c r="W26" s="143"/>
-      <c r="X26" s="143"/>
-      <c r="Y26" s="143"/>
-      <c r="Z26" s="144"/>
+      <c r="C26" s="141"/>
+      <c r="D26" s="141"/>
+      <c r="E26" s="141"/>
+      <c r="F26" s="142"/>
+      <c r="G26" s="142"/>
+      <c r="H26" s="142"/>
+      <c r="I26" s="142"/>
+      <c r="J26" s="142"/>
+      <c r="K26" s="142"/>
+      <c r="L26" s="142"/>
+      <c r="M26" s="142"/>
+      <c r="N26" s="142"/>
+      <c r="O26" s="142"/>
+      <c r="P26" s="142"/>
+      <c r="Q26" s="142"/>
+      <c r="R26" s="142"/>
+      <c r="S26" s="142"/>
+      <c r="T26" s="142"/>
+      <c r="U26" s="142"/>
+      <c r="V26" s="142"/>
+      <c r="W26" s="142"/>
+      <c r="X26" s="142"/>
+      <c r="Y26" s="142"/>
+      <c r="Z26" s="143"/>
     </row>
     <row r="27" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="124" t="s">
@@ -5965,19 +5787,19 @@
       <c r="Z27" s="124"/>
     </row>
     <row r="28" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="145" t="s">
+      <c r="B28" s="144" t="s">
         <v>503</v>
       </c>
-      <c r="C28" s="145"/>
-      <c r="D28" s="145"/>
-      <c r="E28" s="145"/>
-      <c r="F28" s="145"/>
-      <c r="G28" s="145"/>
-      <c r="H28" s="145"/>
-      <c r="I28" s="145"/>
-      <c r="J28" s="145"/>
-      <c r="K28" s="145"/>
-      <c r="L28" s="145"/>
+      <c r="C28" s="144"/>
+      <c r="D28" s="144"/>
+      <c r="E28" s="144"/>
+      <c r="F28" s="144"/>
+      <c r="G28" s="144"/>
+      <c r="H28" s="144"/>
+      <c r="I28" s="144"/>
+      <c r="J28" s="144"/>
+      <c r="K28" s="144"/>
+      <c r="L28" s="144"/>
       <c r="M28" s="135"/>
       <c r="N28" s="136"/>
       <c r="O28" s="136"/>
@@ -6022,679 +5844,119 @@
       <c r="Y29" s="124"/>
       <c r="Z29" s="124"/>
     </row>
-    <row r="30" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="B30" s="138"/>
-      <c r="C30" s="138"/>
-      <c r="D30" s="138"/>
-      <c r="E30" s="138"/>
-      <c r="F30" s="138"/>
-      <c r="G30" s="138"/>
-      <c r="H30" s="138"/>
-      <c r="I30" s="138"/>
-      <c r="J30" s="138"/>
-      <c r="K30" s="138"/>
-      <c r="L30" s="138"/>
-      <c r="M30" s="138"/>
-      <c r="N30" s="138"/>
-      <c r="O30" s="138"/>
-      <c r="P30" s="138"/>
-      <c r="Q30" s="138"/>
-      <c r="R30" s="138"/>
-      <c r="S30" s="138"/>
-      <c r="T30" s="138"/>
-      <c r="U30" s="138"/>
-      <c r="V30" s="138"/>
-      <c r="W30" s="138"/>
-      <c r="X30" s="138"/>
-      <c r="Y30" s="138"/>
-      <c r="Z30" s="138"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="3"/>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="B31" s="138"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="138"/>
-      <c r="E31" s="138"/>
-      <c r="F31" s="138"/>
-      <c r="G31" s="138"/>
-      <c r="H31" s="138"/>
-      <c r="I31" s="138"/>
-      <c r="J31" s="138"/>
-      <c r="K31" s="138"/>
-      <c r="L31" s="138"/>
-      <c r="M31" s="138"/>
-      <c r="N31" s="138"/>
-      <c r="O31" s="138"/>
-      <c r="P31" s="138"/>
-      <c r="Q31" s="138"/>
-      <c r="R31" s="138"/>
-      <c r="S31" s="138"/>
-      <c r="T31" s="138"/>
-      <c r="U31" s="138"/>
-      <c r="V31" s="138"/>
-      <c r="W31" s="138"/>
-      <c r="X31" s="138"/>
-      <c r="Y31" s="138"/>
-      <c r="Z31" s="138"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
+      <c r="Y31" s="3"/>
+      <c r="Z31" s="3"/>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
-      <c r="B32" s="138"/>
-      <c r="C32" s="138"/>
-      <c r="D32" s="138"/>
-      <c r="E32" s="138"/>
-      <c r="F32" s="138"/>
-      <c r="G32" s="138"/>
-      <c r="H32" s="138"/>
-      <c r="I32" s="138"/>
-      <c r="J32" s="138"/>
-      <c r="K32" s="138"/>
-      <c r="L32" s="138"/>
-      <c r="M32" s="138"/>
-      <c r="N32" s="138"/>
-      <c r="O32" s="138"/>
-      <c r="P32" s="138"/>
-      <c r="Q32" s="138"/>
-      <c r="R32" s="138"/>
-      <c r="S32" s="138"/>
-      <c r="T32" s="138"/>
-      <c r="U32" s="138"/>
-      <c r="V32" s="138"/>
-      <c r="W32" s="138"/>
-      <c r="X32" s="138"/>
-      <c r="Y32" s="138"/>
-      <c r="Z32" s="138"/>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A33" s="1"/>
-      <c r="B33" s="138"/>
-      <c r="C33" s="138"/>
-      <c r="D33" s="138"/>
-      <c r="E33" s="138"/>
-      <c r="F33" s="138"/>
-      <c r="G33" s="138"/>
-      <c r="H33" s="138"/>
-      <c r="I33" s="138"/>
-      <c r="J33" s="138"/>
-      <c r="K33" s="138"/>
-      <c r="L33" s="138"/>
-      <c r="M33" s="138"/>
-      <c r="N33" s="138"/>
-      <c r="O33" s="138"/>
-      <c r="P33" s="138"/>
-      <c r="Q33" s="138"/>
-      <c r="R33" s="138"/>
-      <c r="S33" s="138"/>
-      <c r="T33" s="138"/>
-      <c r="U33" s="138"/>
-      <c r="V33" s="138"/>
-      <c r="W33" s="138"/>
-      <c r="X33" s="138"/>
-      <c r="Y33" s="138"/>
-      <c r="Z33" s="138"/>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A34" s="1"/>
-      <c r="B34" s="138"/>
-      <c r="C34" s="138"/>
-      <c r="D34" s="138"/>
-      <c r="E34" s="138"/>
-      <c r="F34" s="138"/>
-      <c r="G34" s="138"/>
-      <c r="H34" s="138"/>
-      <c r="I34" s="138"/>
-      <c r="J34" s="138"/>
-      <c r="K34" s="138"/>
-      <c r="L34" s="138"/>
-      <c r="M34" s="138"/>
-      <c r="N34" s="138"/>
-      <c r="O34" s="138"/>
-      <c r="P34" s="138"/>
-      <c r="Q34" s="138"/>
-      <c r="R34" s="138"/>
-      <c r="S34" s="138"/>
-      <c r="T34" s="138"/>
-      <c r="U34" s="138"/>
-      <c r="V34" s="138"/>
-      <c r="W34" s="138"/>
-      <c r="X34" s="138"/>
-      <c r="Y34" s="138"/>
-      <c r="Z34" s="138"/>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A35" s="1"/>
-      <c r="B35" s="138"/>
-      <c r="C35" s="138"/>
-      <c r="D35" s="138"/>
-      <c r="E35" s="138"/>
-      <c r="F35" s="138"/>
-      <c r="G35" s="138"/>
-      <c r="H35" s="138"/>
-      <c r="I35" s="138"/>
-      <c r="J35" s="138"/>
-      <c r="K35" s="138"/>
-      <c r="L35" s="138"/>
-      <c r="M35" s="138"/>
-      <c r="N35" s="138"/>
-      <c r="O35" s="138"/>
-      <c r="P35" s="138"/>
-      <c r="Q35" s="138"/>
-      <c r="R35" s="138"/>
-      <c r="S35" s="138"/>
-      <c r="T35" s="138"/>
-      <c r="U35" s="138"/>
-      <c r="V35" s="138"/>
-      <c r="W35" s="138"/>
-      <c r="X35" s="138"/>
-      <c r="Y35" s="138"/>
-      <c r="Z35" s="138"/>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A36" s="1"/>
-      <c r="B36" s="138"/>
-      <c r="C36" s="138"/>
-      <c r="D36" s="138"/>
-      <c r="E36" s="138"/>
-      <c r="F36" s="138"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="138"/>
-      <c r="I36" s="138"/>
-      <c r="J36" s="138"/>
-      <c r="K36" s="138"/>
-      <c r="L36" s="138"/>
-      <c r="M36" s="138"/>
-      <c r="N36" s="138"/>
-      <c r="O36" s="138"/>
-      <c r="P36" s="138"/>
-      <c r="Q36" s="138"/>
-      <c r="R36" s="138"/>
-      <c r="S36" s="138"/>
-      <c r="T36" s="138"/>
-      <c r="U36" s="138"/>
-      <c r="V36" s="138"/>
-      <c r="W36" s="138"/>
-      <c r="X36" s="138"/>
-      <c r="Y36" s="138"/>
-      <c r="Z36" s="138"/>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A37" s="1"/>
-      <c r="B37" s="138"/>
-      <c r="C37" s="138"/>
-      <c r="D37" s="138"/>
-      <c r="E37" s="138"/>
-      <c r="F37" s="138"/>
-      <c r="G37" s="138"/>
-      <c r="H37" s="138"/>
-      <c r="I37" s="138"/>
-      <c r="J37" s="138"/>
-      <c r="K37" s="138"/>
-      <c r="L37" s="138"/>
-      <c r="M37" s="138"/>
-      <c r="N37" s="138"/>
-      <c r="O37" s="138"/>
-      <c r="P37" s="138"/>
-      <c r="Q37" s="138"/>
-      <c r="R37" s="138"/>
-      <c r="S37" s="138"/>
-      <c r="T37" s="138"/>
-      <c r="U37" s="138"/>
-      <c r="V37" s="138"/>
-      <c r="W37" s="138"/>
-      <c r="X37" s="138"/>
-      <c r="Y37" s="138"/>
-      <c r="Z37" s="138"/>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A38" s="1"/>
-      <c r="B38" s="138"/>
-      <c r="C38" s="138"/>
-      <c r="D38" s="138"/>
-      <c r="E38" s="138"/>
-      <c r="F38" s="138"/>
-      <c r="G38" s="138"/>
-      <c r="H38" s="138"/>
-      <c r="I38" s="138"/>
-      <c r="J38" s="138"/>
-      <c r="K38" s="138"/>
-      <c r="L38" s="138"/>
-      <c r="M38" s="138"/>
-      <c r="N38" s="138"/>
-      <c r="O38" s="138"/>
-      <c r="P38" s="138"/>
-      <c r="Q38" s="138"/>
-      <c r="R38" s="138"/>
-      <c r="S38" s="138"/>
-      <c r="T38" s="138"/>
-      <c r="U38" s="138"/>
-      <c r="V38" s="138"/>
-      <c r="W38" s="138"/>
-      <c r="X38" s="138"/>
-      <c r="Y38" s="138"/>
-      <c r="Z38" s="138"/>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A39" s="1"/>
-      <c r="B39" s="138"/>
-      <c r="C39" s="138"/>
-      <c r="D39" s="138"/>
-      <c r="E39" s="138"/>
-      <c r="F39" s="138"/>
-      <c r="G39" s="138"/>
-      <c r="H39" s="138"/>
-      <c r="I39" s="138"/>
-      <c r="J39" s="138"/>
-      <c r="K39" s="138"/>
-      <c r="L39" s="138"/>
-      <c r="M39" s="138"/>
-      <c r="N39" s="138"/>
-      <c r="O39" s="138"/>
-      <c r="P39" s="138"/>
-      <c r="Q39" s="138"/>
-      <c r="R39" s="138"/>
-      <c r="S39" s="138"/>
-      <c r="T39" s="138"/>
-      <c r="U39" s="138"/>
-      <c r="V39" s="138"/>
-      <c r="W39" s="138"/>
-      <c r="X39" s="138"/>
-      <c r="Y39" s="138"/>
-      <c r="Z39" s="138"/>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A40" s="1"/>
-      <c r="B40" s="138"/>
-      <c r="C40" s="138"/>
-      <c r="D40" s="138"/>
-      <c r="E40" s="138"/>
-      <c r="F40" s="138"/>
-      <c r="G40" s="138"/>
-      <c r="H40" s="138"/>
-      <c r="I40" s="138"/>
-      <c r="J40" s="138"/>
-      <c r="K40" s="138"/>
-      <c r="L40" s="138"/>
-      <c r="M40" s="138"/>
-      <c r="N40" s="138"/>
-      <c r="O40" s="138"/>
-      <c r="P40" s="138"/>
-      <c r="Q40" s="138"/>
-      <c r="R40" s="138"/>
-      <c r="S40" s="138"/>
-      <c r="T40" s="138"/>
-      <c r="U40" s="138"/>
-      <c r="V40" s="138"/>
-      <c r="W40" s="138"/>
-      <c r="X40" s="138"/>
-      <c r="Y40" s="138"/>
-      <c r="Z40" s="138"/>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A41" s="1"/>
-      <c r="B41" s="138"/>
-      <c r="C41" s="138"/>
-      <c r="D41" s="138"/>
-      <c r="E41" s="138"/>
-      <c r="F41" s="138"/>
-      <c r="G41" s="138"/>
-      <c r="H41" s="138"/>
-      <c r="I41" s="138"/>
-      <c r="J41" s="138"/>
-      <c r="K41" s="138"/>
-      <c r="L41" s="138"/>
-      <c r="M41" s="138"/>
-      <c r="N41" s="138"/>
-      <c r="O41" s="138"/>
-      <c r="P41" s="138"/>
-      <c r="Q41" s="138"/>
-      <c r="R41" s="138"/>
-      <c r="S41" s="138"/>
-      <c r="T41" s="138"/>
-      <c r="U41" s="138"/>
-      <c r="V41" s="138"/>
-      <c r="W41" s="138"/>
-      <c r="X41" s="138"/>
-      <c r="Y41" s="138"/>
-      <c r="Z41" s="138"/>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A42" s="1"/>
-      <c r="B42" s="138"/>
-      <c r="C42" s="138"/>
-      <c r="D42" s="138"/>
-      <c r="E42" s="138"/>
-      <c r="F42" s="138"/>
-      <c r="G42" s="138"/>
-      <c r="H42" s="138"/>
-      <c r="I42" s="138"/>
-      <c r="J42" s="138"/>
-      <c r="K42" s="138"/>
-      <c r="L42" s="138"/>
-      <c r="M42" s="138"/>
-      <c r="N42" s="138"/>
-      <c r="O42" s="138"/>
-      <c r="P42" s="138"/>
-      <c r="Q42" s="138"/>
-      <c r="R42" s="138"/>
-      <c r="S42" s="138"/>
-      <c r="T42" s="138"/>
-      <c r="U42" s="138"/>
-      <c r="V42" s="138"/>
-      <c r="W42" s="138"/>
-      <c r="X42" s="138"/>
-      <c r="Y42" s="138"/>
-      <c r="Z42" s="138"/>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A43" s="1"/>
-      <c r="B43" s="138"/>
-      <c r="C43" s="138"/>
-      <c r="D43" s="138"/>
-      <c r="E43" s="138"/>
-      <c r="F43" s="138"/>
-      <c r="G43" s="138"/>
-      <c r="H43" s="138"/>
-      <c r="I43" s="138"/>
-      <c r="J43" s="138"/>
-      <c r="K43" s="138"/>
-      <c r="L43" s="138"/>
-      <c r="M43" s="138"/>
-      <c r="N43" s="138"/>
-      <c r="O43" s="138"/>
-      <c r="P43" s="138"/>
-      <c r="Q43" s="138"/>
-      <c r="R43" s="138"/>
-      <c r="S43" s="138"/>
-      <c r="T43" s="138"/>
-      <c r="U43" s="138"/>
-      <c r="V43" s="138"/>
-      <c r="W43" s="138"/>
-      <c r="X43" s="138"/>
-      <c r="Y43" s="138"/>
-      <c r="Z43" s="138"/>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A44" s="1"/>
-      <c r="B44" s="138"/>
-      <c r="C44" s="138"/>
-      <c r="D44" s="138"/>
-      <c r="E44" s="138"/>
-      <c r="F44" s="138"/>
-      <c r="G44" s="138"/>
-      <c r="H44" s="138"/>
-      <c r="I44" s="138"/>
-      <c r="J44" s="138"/>
-      <c r="K44" s="138"/>
-      <c r="L44" s="138"/>
-      <c r="M44" s="138"/>
-      <c r="N44" s="138"/>
-      <c r="O44" s="138"/>
-      <c r="P44" s="138"/>
-      <c r="Q44" s="138"/>
-      <c r="R44" s="138"/>
-      <c r="S44" s="138"/>
-      <c r="T44" s="138"/>
-      <c r="U44" s="138"/>
-      <c r="V44" s="138"/>
-      <c r="W44" s="138"/>
-      <c r="X44" s="138"/>
-      <c r="Y44" s="138"/>
-      <c r="Z44" s="138"/>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A45" s="1"/>
-      <c r="B45" s="138"/>
-      <c r="C45" s="138"/>
-      <c r="D45" s="138"/>
-      <c r="E45" s="138"/>
-      <c r="F45" s="138"/>
-      <c r="G45" s="138"/>
-      <c r="H45" s="138"/>
-      <c r="I45" s="138"/>
-      <c r="J45" s="138"/>
-      <c r="K45" s="138"/>
-      <c r="L45" s="138"/>
-      <c r="M45" s="138"/>
-      <c r="N45" s="138"/>
-      <c r="O45" s="138"/>
-      <c r="P45" s="138"/>
-      <c r="Q45" s="138"/>
-      <c r="R45" s="138"/>
-      <c r="S45" s="138"/>
-      <c r="T45" s="138"/>
-      <c r="U45" s="138"/>
-      <c r="V45" s="138"/>
-      <c r="W45" s="138"/>
-      <c r="X45" s="138"/>
-      <c r="Y45" s="138"/>
-      <c r="Z45" s="138"/>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A46" s="1"/>
-      <c r="B46" s="138"/>
-      <c r="C46" s="138"/>
-      <c r="D46" s="138"/>
-      <c r="E46" s="138"/>
-      <c r="F46" s="138"/>
-      <c r="G46" s="138"/>
-      <c r="H46" s="138"/>
-      <c r="I46" s="138"/>
-      <c r="J46" s="138"/>
-      <c r="K46" s="138"/>
-      <c r="L46" s="138"/>
-      <c r="M46" s="138"/>
-      <c r="N46" s="138"/>
-      <c r="O46" s="138"/>
-      <c r="P46" s="138"/>
-      <c r="Q46" s="138"/>
-      <c r="R46" s="138"/>
-      <c r="S46" s="138"/>
-      <c r="T46" s="138"/>
-      <c r="U46" s="138"/>
-      <c r="V46" s="138"/>
-      <c r="W46" s="138"/>
-      <c r="X46" s="138"/>
-      <c r="Y46" s="138"/>
-      <c r="Z46" s="138"/>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A47" s="1"/>
-      <c r="B47" s="138"/>
-      <c r="C47" s="138"/>
-      <c r="D47" s="138"/>
-      <c r="E47" s="138"/>
-      <c r="F47" s="138"/>
-      <c r="G47" s="138"/>
-      <c r="H47" s="138"/>
-      <c r="I47" s="138"/>
-      <c r="J47" s="138"/>
-      <c r="K47" s="138"/>
-      <c r="L47" s="138"/>
-      <c r="M47" s="138"/>
-      <c r="N47" s="138"/>
-      <c r="O47" s="138"/>
-      <c r="P47" s="138"/>
-      <c r="Q47" s="138"/>
-      <c r="R47" s="138"/>
-      <c r="S47" s="138"/>
-      <c r="T47" s="138"/>
-      <c r="U47" s="138"/>
-      <c r="V47" s="138"/>
-      <c r="W47" s="138"/>
-      <c r="X47" s="138"/>
-      <c r="Y47" s="138"/>
-      <c r="Z47" s="138"/>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A48" s="1"/>
-      <c r="B48" s="138"/>
-      <c r="C48" s="138"/>
-      <c r="D48" s="138"/>
-      <c r="E48" s="138"/>
-      <c r="F48" s="138"/>
-      <c r="G48" s="138"/>
-      <c r="H48" s="138"/>
-      <c r="I48" s="138"/>
-      <c r="J48" s="138"/>
-      <c r="K48" s="138"/>
-      <c r="L48" s="138"/>
-      <c r="M48" s="138"/>
-      <c r="N48" s="138"/>
-      <c r="O48" s="138"/>
-      <c r="P48" s="138"/>
-      <c r="Q48" s="138"/>
-      <c r="R48" s="138"/>
-      <c r="S48" s="138"/>
-      <c r="T48" s="138"/>
-      <c r="U48" s="138"/>
-      <c r="V48" s="138"/>
-      <c r="W48" s="138"/>
-      <c r="X48" s="138"/>
-      <c r="Y48" s="138"/>
-      <c r="Z48" s="138"/>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A49" s="1"/>
-      <c r="B49" s="138"/>
-      <c r="C49" s="138"/>
-      <c r="D49" s="138"/>
-      <c r="E49" s="138"/>
-      <c r="F49" s="138"/>
-      <c r="G49" s="138"/>
-      <c r="H49" s="138"/>
-      <c r="I49" s="138"/>
-      <c r="J49" s="138"/>
-      <c r="K49" s="138"/>
-      <c r="L49" s="138"/>
-      <c r="M49" s="138"/>
-      <c r="N49" s="138"/>
-      <c r="O49" s="138"/>
-      <c r="P49" s="138"/>
-      <c r="Q49" s="138"/>
-      <c r="R49" s="138"/>
-      <c r="S49" s="138"/>
-      <c r="T49" s="138"/>
-      <c r="U49" s="138"/>
-      <c r="V49" s="138"/>
-      <c r="W49" s="138"/>
-      <c r="X49" s="138"/>
-      <c r="Y49" s="138"/>
-      <c r="Z49" s="138"/>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A50" s="1"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
-      <c r="R50" s="3"/>
-      <c r="S50" s="3"/>
-      <c r="T50" s="3"/>
-      <c r="U50" s="3"/>
-      <c r="V50" s="3"/>
-      <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="3"/>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A51" s="1"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="3"/>
-      <c r="Q51" s="3"/>
-      <c r="R51" s="3"/>
-      <c r="S51" s="3"/>
-      <c r="T51" s="3"/>
-      <c r="U51" s="3"/>
-      <c r="V51" s="3"/>
-      <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="3"/>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A52" s="1"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-      <c r="O52" s="3"/>
-      <c r="P52" s="3"/>
-      <c r="Q52" s="3"/>
-      <c r="R52" s="3"/>
-      <c r="S52" s="3"/>
-      <c r="T52" s="3"/>
-      <c r="U52" s="3"/>
-      <c r="V52" s="3"/>
-      <c r="W52" s="3"/>
-      <c r="X52" s="3"/>
-      <c r="Y52" s="3"/>
-      <c r="Z52" s="3"/>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
-      <c r="O53" s="3"/>
-      <c r="P53" s="3"/>
-      <c r="Q53" s="3"/>
-      <c r="R53" s="3"/>
-      <c r="S53" s="3"/>
-      <c r="T53" s="3"/>
-      <c r="U53" s="3"/>
-      <c r="V53" s="3"/>
-      <c r="W53" s="3"/>
-      <c r="X53" s="3"/>
-      <c r="Y53" s="3"/>
-      <c r="Z53" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="3"/>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="3"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
+      <c r="U33" s="3"/>
+      <c r="V33" s="3"/>
+      <c r="W33" s="3"/>
+      <c r="X33" s="3"/>
+      <c r="Y33" s="3"/>
+      <c r="Z33" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="70">
+  <mergeCells count="69">
     <mergeCell ref="C8:L8"/>
     <mergeCell ref="M23:O23"/>
     <mergeCell ref="F25:O25"/>
@@ -6711,6 +5973,15 @@
     <mergeCell ref="C15:L15"/>
     <mergeCell ref="B14:Z14"/>
     <mergeCell ref="B18:E18"/>
+    <mergeCell ref="C7:L7"/>
+    <mergeCell ref="N7:R7"/>
+    <mergeCell ref="F18:Z18"/>
+    <mergeCell ref="N8:R8"/>
+    <mergeCell ref="Q4:U4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="S8:V8"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="O15:Q15"/>
     <mergeCell ref="R17:V17"/>
     <mergeCell ref="B10:Z10"/>
     <mergeCell ref="C11:L11"/>
@@ -6718,13 +5989,9 @@
     <mergeCell ref="S11:V11"/>
     <mergeCell ref="M17:N17"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="F18:Z18"/>
-    <mergeCell ref="N8:R8"/>
-    <mergeCell ref="Q4:U4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="S8:V8"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="B29:Z29"/>
+    <mergeCell ref="Y25:Z25"/>
+    <mergeCell ref="M28:Z28"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:W2"/>
     <mergeCell ref="W7:Z7"/>
@@ -6738,17 +6005,11 @@
     <mergeCell ref="N4:P4"/>
     <mergeCell ref="N3:P3"/>
     <mergeCell ref="S7:V7"/>
-    <mergeCell ref="C7:L7"/>
-    <mergeCell ref="N7:R7"/>
-    <mergeCell ref="B30:Z49"/>
     <mergeCell ref="U25:W25"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="F26:Z26"/>
     <mergeCell ref="B27:Z27"/>
     <mergeCell ref="B28:L28"/>
-    <mergeCell ref="B29:Z29"/>
-    <mergeCell ref="Y25:Z25"/>
-    <mergeCell ref="M28:Z28"/>
     <mergeCell ref="B24:Z24"/>
     <mergeCell ref="F23:L23"/>
     <mergeCell ref="W16:X16"/>
@@ -6770,40 +6031,9 @@
   <pageMargins left="0" right="0" top="0.31496062992125984" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
-          <x14:formula1>
-            <xm:f>Tablas!$Z$9:$Z$11</xm:f>
-          </x14:formula1>
-          <xm:sqref>Y16</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
-          <x14:formula1>
-            <xm:f>Tablas!$AJ$3:$AJ$5</xm:f>
-          </x14:formula1>
-          <xm:sqref>Q16</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000006000000}">
-          <x14:formula1>
-            <xm:f>Tablas!$A$4:$A$27</xm:f>
-          </x14:formula1>
-          <xm:sqref>C15</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000005000000}">
-          <x14:formula1>
-            <xm:f>Tablas!$X$9:$X$13</xm:f>
-          </x14:formula1>
-          <xm:sqref>O15</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{95073319-ECCC-4CC9-B2BF-A8EFF9936E5C}">
-          <x14:formula1>
-            <xm:f>Tablas!$X$18:$X$23</xm:f>
-          </x14:formula1>
-          <xm:sqref>W17</xm:sqref>
-        </x14:dataValidation>
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{72572276-1F3B-4AEE-8549-42EDA16047A8}">
           <x14:formula1>
             <xm:f>'C:\Users\kevin\Downloads\[ReportePreliminarIncidente-18052020193420.xlsx]Tablas'!#REF!</xm:f>
@@ -6886,29 +6116,29 @@
         <v>405</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="191" t="s">
+      <c r="C2" s="189" t="s">
         <v>432</v>
       </c>
-      <c r="D2" s="193"/>
-      <c r="E2" s="193"/>
-      <c r="F2" s="193"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
       <c r="G2" s="7"/>
-      <c r="H2" s="191" t="s">
+      <c r="H2" s="189" t="s">
         <v>433</v>
       </c>
-      <c r="I2" s="193"/>
-      <c r="J2" s="193"/>
-      <c r="K2" s="193"/>
-      <c r="M2" s="191" t="s">
+      <c r="I2" s="191"/>
+      <c r="J2" s="191"/>
+      <c r="K2" s="191"/>
+      <c r="M2" s="189" t="s">
         <v>375</v>
       </c>
-      <c r="N2" s="191"/>
-      <c r="O2" s="191"/>
-      <c r="P2" s="191"/>
-      <c r="Q2" s="191"/>
-      <c r="R2" s="191"/>
-      <c r="S2" s="191"/>
-      <c r="T2" s="191"/>
+      <c r="N2" s="189"/>
+      <c r="O2" s="189"/>
+      <c r="P2" s="189"/>
+      <c r="Q2" s="189"/>
+      <c r="R2" s="189"/>
+      <c r="S2" s="189"/>
+      <c r="T2" s="189"/>
       <c r="U2" s="7"/>
       <c r="V2" s="66" t="s">
         <v>434</v>
@@ -6940,23 +6170,23 @@
         <v>21</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="194" t="s">
+      <c r="C3" s="192" t="s">
         <v>373</v>
       </c>
-      <c r="D3" s="195"/>
-      <c r="E3" s="194" t="s">
+      <c r="D3" s="193"/>
+      <c r="E3" s="192" t="s">
         <v>374</v>
       </c>
-      <c r="F3" s="195"/>
+      <c r="F3" s="193"/>
       <c r="G3" s="7"/>
-      <c r="H3" s="192" t="s">
+      <c r="H3" s="190" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="192"/>
-      <c r="J3" s="192" t="s">
+      <c r="I3" s="190"/>
+      <c r="J3" s="190" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="192"/>
+      <c r="K3" s="190"/>
       <c r="M3" s="72">
         <v>1</v>
       </c>

--- a/GestionAmbiental/wwwroot/ExcelTemplates/Incidentes/ReportePreliminar/JU-MAP-STD-001.F01_Reporte preliminar de incidente ambiental_V00.xlsx
+++ b/GestionAmbiental/wwwroot/ExcelTemplates/Incidentes/ReportePreliminar/JU-MAP-STD-001.F01_Reporte preliminar de incidente ambiental_V00.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Electrodata\Marcobre\Gestiona Marcobre\Marcobre-GestionAmbiental\GestionAmbiental\wwwroot\ExcelTemplates\Incidentes\ReportePreliminar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8683D5F-87D2-4FBD-9B42-1A808A45A3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4071A8FD-BA66-4F89-9766-E6B723EE374E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3500" yWindow="8980" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RPIA" sheetId="3" r:id="rId1"/>
@@ -1915,9 +1915,6 @@
     <t>Área:</t>
   </si>
   <si>
-    <t>Gerencia de Medio Ambiente y Permisos</t>
-  </si>
-  <si>
     <t>Código:</t>
   </si>
   <si>
@@ -3228,9 +3225,6 @@
     <t>N.A.</t>
   </si>
   <si>
-    <t>REPORTE PRELIMINAR DEL INCIDENTE AMBIENTAL</t>
-  </si>
-  <si>
     <t>MAA01. Afectar a la flora/fauna/sitios arqueológicos.</t>
   </si>
   <si>
@@ -3487,6 +3481,12 @@
   </si>
   <si>
     <t>Acción Preventiva o Correctiva</t>
+  </si>
+  <si>
+    <t>Gerencia de Medio Ambiente</t>
+  </si>
+  <si>
+    <t>REPORTE DE INCIDENTE MENOR</t>
   </si>
 </sst>
 </file>
@@ -4339,20 +4339,20 @@
     <xf numFmtId="14" fontId="3" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4892,7 +4892,7 @@
       <c r="A2" s="1"/>
       <c r="B2" s="147"/>
       <c r="C2" s="148" t="s">
-        <v>439</v>
+        <v>525</v>
       </c>
       <c r="D2" s="148"/>
       <c r="E2" s="148"/>
@@ -4922,11 +4922,11 @@
       <c r="A3" s="1"/>
       <c r="B3" s="147"/>
       <c r="C3" s="160" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" s="161"/>
       <c r="E3" s="162" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F3" s="162"/>
       <c r="G3" s="162"/>
@@ -4935,19 +4935,19 @@
       <c r="J3" s="162"/>
       <c r="K3" s="163"/>
       <c r="L3" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M3" s="5"/>
       <c r="N3" s="169">
-        <v>43831</v>
+        <v>45931</v>
       </c>
       <c r="O3" s="167"/>
       <c r="P3" s="168"/>
       <c r="Q3" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S3" s="149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" s="149"/>
       <c r="U3" s="149"/>
@@ -4964,7 +4964,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="164" t="s">
-        <v>16</v>
+        <v>524</v>
       </c>
       <c r="E4" s="164"/>
       <c r="F4" s="164"/>
@@ -4983,14 +4983,14 @@
       <c r="O4" s="167"/>
       <c r="P4" s="168"/>
       <c r="Q4" s="111" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R4" s="112"/>
       <c r="S4" s="112"/>
       <c r="T4" s="112"/>
       <c r="U4" s="112"/>
       <c r="V4" s="137">
-        <v>43818</v>
+        <v>45919</v>
       </c>
       <c r="W4" s="123"/>
       <c r="X4" s="157"/>
@@ -5027,7 +5027,7 @@
     </row>
     <row r="6" spans="1:26" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="141" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C6" s="141"/>
       <c r="D6" s="141"/>
@@ -5056,10 +5056,10 @@
     </row>
     <row r="7" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="98" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C7" s="134" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D7" s="134"/>
       <c r="E7" s="134"/>
@@ -5071,7 +5071,7 @@
       <c r="K7" s="134"/>
       <c r="L7" s="134"/>
       <c r="M7" s="56" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N7" s="135">
         <v>20508972734</v>
@@ -5081,13 +5081,13 @@
       <c r="Q7" s="135"/>
       <c r="R7" s="135"/>
       <c r="S7" s="142" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="T7" s="142"/>
       <c r="U7" s="142"/>
       <c r="V7" s="142"/>
       <c r="W7" s="121" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="X7" s="122"/>
       <c r="Y7" s="122"/>
@@ -5095,10 +5095,10 @@
     </row>
     <row r="8" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="48" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C8" s="111" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D8" s="112"/>
       <c r="E8" s="112"/>
@@ -5110,17 +5110,17 @@
       <c r="K8" s="112"/>
       <c r="L8" s="113"/>
       <c r="M8" s="95" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N8" s="136" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="O8" s="136"/>
       <c r="P8" s="136"/>
       <c r="Q8" s="136"/>
       <c r="R8" s="136"/>
       <c r="S8" s="124" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="T8" s="124"/>
       <c r="U8" s="124"/>
@@ -5160,7 +5160,7 @@
     </row>
     <row r="10" spans="1:26" ht="23.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="141" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C10" s="141"/>
       <c r="D10" s="141"/>
@@ -5189,7 +5189,7 @@
     </row>
     <row r="11" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="98" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C11" s="136"/>
       <c r="D11" s="136"/>
@@ -5202,7 +5202,7 @@
       <c r="K11" s="136"/>
       <c r="L11" s="136"/>
       <c r="M11" s="56" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="N11" s="135"/>
       <c r="O11" s="135"/>
@@ -5210,7 +5210,7 @@
       <c r="Q11" s="135"/>
       <c r="R11" s="135"/>
       <c r="S11" s="142" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="T11" s="142"/>
       <c r="U11" s="142"/>
@@ -5222,7 +5222,7 @@
     </row>
     <row r="12" spans="1:26" ht="26.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="48" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C12" s="121"/>
       <c r="D12" s="122"/>
@@ -5241,7 +5241,7 @@
       <c r="Q12" s="122"/>
       <c r="R12" s="123"/>
       <c r="S12" s="124" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="T12" s="124"/>
       <c r="U12" s="124"/>
@@ -5280,7 +5280,7 @@
     </row>
     <row r="14" spans="1:26" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="130" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C14" s="130"/>
       <c r="D14" s="130"/>
@@ -5310,7 +5310,7 @@
     <row r="15" spans="1:26" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="47" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C15" s="121"/>
       <c r="D15" s="122"/>
@@ -5323,14 +5323,14 @@
       <c r="K15" s="122"/>
       <c r="L15" s="123"/>
       <c r="M15" s="103" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N15" s="104"/>
       <c r="O15" s="121"/>
       <c r="P15" s="122"/>
       <c r="Q15" s="123"/>
       <c r="R15" s="127" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="S15" s="128"/>
       <c r="T15" s="128"/>
@@ -5338,7 +5338,7 @@
       <c r="V15" s="129"/>
       <c r="W15" s="25"/>
       <c r="X15" s="53" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="Y15" s="125"/>
       <c r="Z15" s="126"/>
@@ -5346,27 +5346,27 @@
     <row r="16" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="54" t="s">
-        <v>427</v>
-      </c>
-      <c r="C16" s="172"/>
-      <c r="D16" s="172"/>
-      <c r="E16" s="172"/>
-      <c r="F16" s="172"/>
-      <c r="G16" s="172"/>
-      <c r="H16" s="172"/>
-      <c r="I16" s="172"/>
-      <c r="J16" s="172"/>
-      <c r="K16" s="172"/>
-      <c r="L16" s="172"/>
+        <v>426</v>
+      </c>
+      <c r="C16" s="173"/>
+      <c r="D16" s="173"/>
+      <c r="E16" s="173"/>
+      <c r="F16" s="173"/>
+      <c r="G16" s="173"/>
+      <c r="H16" s="173"/>
+      <c r="I16" s="173"/>
+      <c r="J16" s="173"/>
+      <c r="K16" s="173"/>
+      <c r="L16" s="173"/>
       <c r="M16" s="143" t="s">
-        <v>420</v>
-      </c>
-      <c r="N16" s="173"/>
+        <v>419</v>
+      </c>
+      <c r="N16" s="174"/>
       <c r="O16" s="136"/>
       <c r="P16" s="136"/>
       <c r="Q16" s="99"/>
       <c r="R16" s="92" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="S16" s="93"/>
       <c r="T16" s="93"/>
@@ -5379,7 +5379,7 @@
     </row>
     <row r="17" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="48" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C17" s="145"/>
       <c r="D17" s="145"/>
@@ -5392,14 +5392,14 @@
       <c r="K17" s="145"/>
       <c r="L17" s="145"/>
       <c r="M17" s="143" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="N17" s="144"/>
-      <c r="O17" s="172"/>
-      <c r="P17" s="172"/>
-      <c r="Q17" s="172"/>
+      <c r="O17" s="173"/>
+      <c r="P17" s="173"/>
+      <c r="Q17" s="173"/>
       <c r="R17" s="138" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="S17" s="139"/>
       <c r="T17" s="139"/>
@@ -5413,7 +5413,7 @@
     <row r="18" spans="1:26" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="131" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C18" s="132"/>
       <c r="D18" s="132"/>
@@ -5443,7 +5443,7 @@
     <row r="19" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="130" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C19" s="130"/>
       <c r="D19" s="130"/>
@@ -5473,13 +5473,13 @@
     <row r="20" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="105" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C20" s="106"/>
       <c r="D20" s="106"/>
       <c r="E20" s="107"/>
       <c r="F20" s="114" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G20" s="114"/>
       <c r="H20" s="114"/>
@@ -5491,7 +5491,7 @@
       <c r="N20" s="114"/>
       <c r="O20" s="114"/>
       <c r="P20" s="114" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Q20" s="114"/>
       <c r="R20" s="114"/>
@@ -5507,7 +5507,7 @@
     <row r="21" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="130" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C21" s="130"/>
       <c r="D21" s="130"/>
@@ -5537,13 +5537,13 @@
     <row r="22" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="105" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C22" s="106"/>
       <c r="D22" s="106"/>
       <c r="E22" s="107"/>
       <c r="F22" s="114" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="G22" s="114"/>
       <c r="H22" s="114"/>
@@ -5555,7 +5555,7 @@
       <c r="N22" s="114"/>
       <c r="O22" s="114"/>
       <c r="P22" s="114" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="Q22" s="114"/>
       <c r="R22" s="114"/>
@@ -5571,7 +5571,7 @@
     <row r="23" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="127" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C23" s="128"/>
       <c r="D23" s="128"/>
@@ -5601,7 +5601,7 @@
     <row r="24" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="130" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C24" s="130"/>
       <c r="D24" s="130"/>
@@ -5630,40 +5630,40 @@
     </row>
     <row r="25" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="B25" s="174" t="s">
+      <c r="B25" s="172" t="s">
+        <v>511</v>
+      </c>
+      <c r="C25" s="172"/>
+      <c r="D25" s="172"/>
+      <c r="E25" s="172"/>
+      <c r="F25" s="172" t="s">
+        <v>512</v>
+      </c>
+      <c r="G25" s="172"/>
+      <c r="H25" s="172"/>
+      <c r="I25" s="172"/>
+      <c r="J25" s="172"/>
+      <c r="K25" s="172"/>
+      <c r="L25" s="172"/>
+      <c r="M25" s="114" t="s">
         <v>513</v>
-      </c>
-      <c r="C25" s="174"/>
-      <c r="D25" s="174"/>
-      <c r="E25" s="174"/>
-      <c r="F25" s="174" t="s">
-        <v>514</v>
-      </c>
-      <c r="G25" s="174"/>
-      <c r="H25" s="174"/>
-      <c r="I25" s="174"/>
-      <c r="J25" s="174"/>
-      <c r="K25" s="174"/>
-      <c r="L25" s="174"/>
-      <c r="M25" s="114" t="s">
-        <v>515</v>
       </c>
       <c r="N25" s="114"/>
       <c r="O25" s="114"/>
       <c r="P25" s="114" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="Q25" s="114"/>
       <c r="R25" s="114"/>
       <c r="S25" s="114"/>
       <c r="T25" s="114"/>
       <c r="U25" s="114" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="V25" s="114"/>
       <c r="W25" s="114"/>
       <c r="X25" s="114" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="Y25" s="114"/>
       <c r="Z25" s="114"/>
@@ -5671,7 +5671,7 @@
     <row r="26" spans="1:26" ht="25.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="130" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C26" s="130"/>
       <c r="D26" s="130"/>
@@ -5701,7 +5701,7 @@
     <row r="27" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="110" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C27" s="108"/>
       <c r="D27" s="108"/>
@@ -5726,7 +5726,7 @@
       <c r="S27" s="116"/>
       <c r="T27" s="117"/>
       <c r="U27" s="115" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="V27" s="116"/>
       <c r="W27" s="117"/>
@@ -5741,13 +5741,13 @@
     <row r="28" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="110" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C28" s="108"/>
       <c r="D28" s="108"/>
       <c r="E28" s="109"/>
       <c r="F28" s="115" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G28" s="116"/>
       <c r="H28" s="116"/>
@@ -5766,7 +5766,7 @@
       <c r="S28" s="116"/>
       <c r="T28" s="117"/>
       <c r="U28" s="115" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="V28" s="116"/>
       <c r="W28" s="117"/>
@@ -5779,12 +5779,12 @@
       <c r="Z28" s="117"/>
     </row>
     <row r="29" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="170" t="s">
-        <v>430</v>
-      </c>
-      <c r="C29" s="170"/>
-      <c r="D29" s="170"/>
-      <c r="E29" s="170"/>
+      <c r="B29" s="171" t="s">
+        <v>429</v>
+      </c>
+      <c r="C29" s="171"/>
+      <c r="D29" s="171"/>
+      <c r="E29" s="171"/>
       <c r="F29" s="122"/>
       <c r="G29" s="122"/>
       <c r="H29" s="122"/>
@@ -5809,7 +5809,7 @@
     </row>
     <row r="30" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="130" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C30" s="130"/>
       <c r="D30" s="130"/>
@@ -5837,19 +5837,19 @@
       <c r="Z30" s="130"/>
     </row>
     <row r="31" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="171" t="s">
-        <v>503</v>
-      </c>
-      <c r="C31" s="171"/>
-      <c r="D31" s="171"/>
-      <c r="E31" s="171"/>
-      <c r="F31" s="171"/>
-      <c r="G31" s="171"/>
-      <c r="H31" s="171"/>
-      <c r="I31" s="171"/>
-      <c r="J31" s="171"/>
-      <c r="K31" s="171"/>
-      <c r="L31" s="171"/>
+      <c r="B31" s="170" t="s">
+        <v>501</v>
+      </c>
+      <c r="C31" s="170"/>
+      <c r="D31" s="170"/>
+      <c r="E31" s="170"/>
+      <c r="F31" s="170"/>
+      <c r="G31" s="170"/>
+      <c r="H31" s="170"/>
+      <c r="I31" s="170"/>
+      <c r="J31" s="170"/>
+      <c r="K31" s="170"/>
+      <c r="L31" s="170"/>
       <c r="M31" s="125"/>
       <c r="N31" s="146"/>
       <c r="O31" s="146"/>
@@ -5867,7 +5867,7 @@
     </row>
     <row r="32" spans="1:26" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="130" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C32" s="130"/>
       <c r="D32" s="130"/>
@@ -6007,9 +6007,6 @@
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="P22:Z22"/>
-    <mergeCell ref="B26:Z26"/>
-    <mergeCell ref="F25:L25"/>
     <mergeCell ref="W16:X16"/>
     <mergeCell ref="Y16:Z16"/>
     <mergeCell ref="C16:L16"/>
@@ -6029,6 +6026,9 @@
     <mergeCell ref="U27:W27"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="F29:Z29"/>
+    <mergeCell ref="P22:Z22"/>
+    <mergeCell ref="B26:Z26"/>
+    <mergeCell ref="F25:L25"/>
     <mergeCell ref="B30:Z30"/>
     <mergeCell ref="B31:L31"/>
     <mergeCell ref="F28:O28"/>
@@ -6169,22 +6169,22 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A2" s="62" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C2" s="175" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D2" s="177"/>
       <c r="E2" s="177"/>
       <c r="F2" s="177"/>
       <c r="H2" s="175" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="I2" s="177"/>
       <c r="J2" s="177"/>
       <c r="K2" s="177"/>
       <c r="M2" s="175" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="N2" s="175"/>
       <c r="O2" s="175"/>
@@ -6194,86 +6194,86 @@
       <c r="S2" s="175"/>
       <c r="T2" s="175"/>
       <c r="V2" s="63" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="X2" s="64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Z2" s="64" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AB2" s="64" t="s">
+        <v>398</v>
+      </c>
+      <c r="AD2" s="65" t="s">
         <v>399</v>
-      </c>
-      <c r="AD2" s="65" t="s">
-        <v>400</v>
       </c>
       <c r="AF2" s="65" t="s">
         <v>12</v>
       </c>
       <c r="AH2" s="66" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AJ2" s="66" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:36" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="67" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C3" s="178" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D3" s="179"/>
       <c r="E3" s="178" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F3" s="179"/>
       <c r="H3" s="176" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I3" s="176"/>
       <c r="J3" s="176" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K3" s="176"/>
       <c r="M3" s="68">
         <v>1</v>
       </c>
       <c r="N3" s="69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O3" s="39"/>
       <c r="P3" s="68">
         <v>1</v>
       </c>
       <c r="Q3" s="69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R3" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S3" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S3" s="72" t="s">
+      <c r="T3" s="72" t="s">
         <v>436</v>
       </c>
-      <c r="T3" s="72" t="s">
-        <v>437</v>
-      </c>
       <c r="V3" s="42" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="X3" s="26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Z3" s="26" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AB3" s="15" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD3" s="45" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AF3" s="6" t="s">
         <v>13</v>
@@ -6288,63 +6288,63 @@
     </row>
     <row r="4" spans="1:36" ht="25.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="14">
         <v>1</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E4" s="14">
         <v>1</v>
       </c>
       <c r="F4" s="96" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="80">
         <v>1</v>
       </c>
       <c r="I4" s="81" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J4" s="82">
         <v>8</v>
       </c>
       <c r="K4" s="81" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L4" s="11"/>
       <c r="M4" s="70">
         <v>2</v>
       </c>
       <c r="N4" s="67" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O4" s="38"/>
       <c r="P4" s="46">
         <v>1.1000000000000001</v>
       </c>
       <c r="Q4" s="36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R4" s="34"/>
       <c r="S4" s="17"/>
       <c r="T4" s="17"/>
       <c r="U4" s="7"/>
       <c r="V4" s="42" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="X4" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Z4" s="26" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AD4" s="45"/>
       <c r="AF4" s="6" t="s">
@@ -6360,119 +6360,119 @@
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A5" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="14">
         <v>2</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E5" s="14">
         <v>2</v>
       </c>
       <c r="F5" s="96" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="25">
         <v>1.1000000000000001</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J5" s="14">
         <v>8.1</v>
       </c>
       <c r="K5" s="26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L5" s="37"/>
       <c r="M5" s="70">
         <v>3</v>
       </c>
       <c r="N5" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O5" s="38"/>
       <c r="P5" s="46">
         <v>1.2</v>
       </c>
       <c r="Q5" s="36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R5" s="35"/>
       <c r="S5" s="18"/>
       <c r="T5" s="18"/>
       <c r="U5" s="7"/>
       <c r="V5" s="42" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="X5" s="26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Z5" s="26" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AH5" s="6" t="s">
         <v>5</v>
       </c>
       <c r="AI5" s="29"/>
       <c r="AJ5" s="91" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A6" s="32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="14">
         <v>3</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E6" s="14">
         <v>3</v>
       </c>
       <c r="F6" s="96" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="25">
         <v>1.2</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J6" s="14">
         <v>8.1999999999999993</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L6" s="37"/>
       <c r="M6" s="70">
         <v>4</v>
       </c>
       <c r="N6" s="67" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="O6" s="38"/>
       <c r="P6" s="46">
         <v>1.3</v>
       </c>
       <c r="Q6" s="36" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R6" s="35"/>
       <c r="S6" s="18"/>
       <c r="T6" s="18"/>
       <c r="U6" s="7"/>
       <c r="V6" s="42" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AH6" s="6" t="s">
         <v>6</v>
@@ -6482,54 +6482,54 @@
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A7" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="14">
         <v>4</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E7" s="14">
         <v>4</v>
       </c>
       <c r="F7" s="96" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="25">
         <v>1.3</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J7" s="14">
         <v>8.3000000000000007</v>
       </c>
       <c r="K7" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L7" s="37"/>
       <c r="M7" s="70">
         <v>5</v>
       </c>
       <c r="N7" s="67" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O7" s="38"/>
       <c r="P7" s="46">
         <v>1.4</v>
       </c>
       <c r="Q7" s="36" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R7" s="35"/>
       <c r="S7" s="18"/>
       <c r="T7" s="18"/>
       <c r="U7" s="7"/>
       <c r="V7" s="42" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Y7" s="8"/>
       <c r="AA7" s="8"/>
@@ -6543,61 +6543,61 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A8" s="32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="14">
         <v>5</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E8" s="14">
         <v>5</v>
       </c>
       <c r="F8" s="96" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="25">
         <v>1.4</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J8" s="14">
         <v>8.4</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L8" s="37"/>
       <c r="M8" s="70">
         <v>6</v>
       </c>
       <c r="N8" s="67" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O8" s="38"/>
       <c r="P8" s="46">
         <v>1.5</v>
       </c>
       <c r="Q8" s="36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R8" s="35"/>
       <c r="S8" s="18"/>
       <c r="T8" s="18"/>
       <c r="U8" s="7"/>
       <c r="V8" s="42" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="X8" s="64" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Y8" s="8"/>
       <c r="Z8" s="64" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AA8" s="8"/>
       <c r="AC8" s="3"/>
@@ -6610,61 +6610,61 @@
     </row>
     <row r="9" spans="1:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="14">
         <v>6</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E9" s="14">
         <v>6</v>
       </c>
       <c r="F9" s="96" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="25">
         <v>1.5</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J9" s="14">
         <v>8.5</v>
       </c>
       <c r="K9" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L9" s="37"/>
       <c r="M9" s="70">
         <v>7</v>
       </c>
       <c r="N9" s="67" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O9" s="38"/>
       <c r="P9" s="46">
         <v>1.6</v>
       </c>
       <c r="Q9" s="36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R9" s="35"/>
       <c r="S9" s="18"/>
       <c r="T9" s="18"/>
       <c r="U9" s="7"/>
       <c r="V9" s="42" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="X9" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Y9" s="8"/>
       <c r="Z9" s="52" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AA9" s="8"/>
       <c r="AB9" s="8"/>
@@ -6673,61 +6673,61 @@
     </row>
     <row r="10" spans="1:36" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="14">
         <v>7</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E10" s="14">
         <v>7</v>
       </c>
       <c r="F10" s="96" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="25">
         <v>1.6</v>
       </c>
       <c r="I10" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J10" s="14">
         <v>8.6</v>
       </c>
       <c r="K10" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L10" s="37"/>
       <c r="M10" s="70">
         <v>8</v>
       </c>
       <c r="N10" s="67" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O10" s="38"/>
       <c r="P10" s="46">
         <v>1.7</v>
       </c>
       <c r="Q10" s="36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R10" s="35"/>
       <c r="S10" s="18"/>
       <c r="T10" s="18"/>
       <c r="U10" s="7"/>
       <c r="V10" s="42" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="X10" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Y10" s="8"/>
       <c r="Z10" s="52" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AA10" s="8"/>
       <c r="AB10" s="8"/>
@@ -6736,61 +6736,61 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A11" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="14">
         <v>8</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E11" s="14">
         <v>8</v>
       </c>
       <c r="F11" s="96" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="25">
         <v>1.7</v>
       </c>
       <c r="I11" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J11" s="14">
         <v>8.6999999999999993</v>
       </c>
       <c r="K11" s="26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L11" s="37"/>
       <c r="M11" s="70">
         <v>9</v>
       </c>
       <c r="N11" s="67" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="O11" s="38"/>
       <c r="P11" s="46">
         <v>1.8</v>
       </c>
       <c r="Q11" s="36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R11" s="35"/>
       <c r="S11" s="18"/>
       <c r="T11" s="18"/>
       <c r="U11" s="7"/>
       <c r="V11" s="42" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="X11" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Y11" s="8"/>
       <c r="Z11" s="52" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AA11" s="8"/>
       <c r="AB11" s="8"/>
@@ -6799,57 +6799,57 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A12" s="32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="14">
         <v>9</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E12" s="14">
         <v>9</v>
       </c>
       <c r="F12" s="96" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="25">
         <v>1.8</v>
       </c>
       <c r="I12" s="26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J12" s="14">
         <v>8.8000000000000007</v>
       </c>
       <c r="K12" s="26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L12" s="37"/>
       <c r="M12" s="70">
         <v>10</v>
       </c>
       <c r="N12" s="67" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O12" s="38"/>
       <c r="P12" s="46">
         <v>1.9</v>
       </c>
       <c r="Q12" s="36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R12" s="35"/>
       <c r="S12" s="18"/>
       <c r="T12" s="18"/>
       <c r="U12" s="7"/>
       <c r="V12" s="43" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="X12" s="46" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Y12" s="8"/>
       <c r="AA12" s="8"/>
@@ -6859,185 +6859,185 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A13" s="32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="14">
         <v>10</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E13" s="14">
         <v>10</v>
       </c>
       <c r="F13" s="96" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="25">
         <v>1.9</v>
       </c>
       <c r="I13" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J13" s="14">
         <v>8.9</v>
       </c>
       <c r="K13" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L13" s="37"/>
       <c r="M13" s="70">
         <v>11</v>
       </c>
       <c r="N13" s="67" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O13" s="38"/>
       <c r="P13" s="87">
         <v>1.1000000000000001</v>
       </c>
       <c r="Q13" s="36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R13" s="35"/>
       <c r="S13" s="18"/>
       <c r="T13" s="18"/>
       <c r="U13" s="7"/>
       <c r="V13" s="42" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="X13" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AC13" s="8"/>
       <c r="AD13" s="8"/>
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A14" s="32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B14" s="7"/>
       <c r="C14" s="14">
         <v>11</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E14" s="14">
         <v>11</v>
       </c>
       <c r="F14" s="96" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="27">
         <v>1.1000000000000001</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J14" s="28">
         <v>8.1</v>
       </c>
       <c r="K14" s="26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L14" s="37"/>
       <c r="M14" s="70">
         <v>12</v>
       </c>
       <c r="N14" s="67" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O14" s="38"/>
       <c r="P14" s="46">
         <v>1.1100000000000001</v>
       </c>
       <c r="Q14" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R14" s="35"/>
       <c r="S14" s="18"/>
       <c r="T14" s="18"/>
       <c r="U14" s="7"/>
       <c r="V14" s="42" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AC14" s="8"/>
       <c r="AD14" s="8"/>
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A15" s="32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="14">
         <v>12</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E15" s="14">
         <v>12</v>
       </c>
       <c r="F15" s="96" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="25">
         <v>1.1100000000000001</v>
       </c>
       <c r="I15" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J15" s="14">
         <v>8.11</v>
       </c>
       <c r="K15" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L15" s="37"/>
       <c r="M15" s="70">
         <v>13</v>
       </c>
       <c r="N15" s="67" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="O15" s="38"/>
       <c r="P15" s="46">
         <v>1.1200000000000001</v>
       </c>
       <c r="Q15" s="36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R15" s="35"/>
       <c r="S15" s="18"/>
       <c r="T15" s="18"/>
       <c r="U15" s="7"/>
       <c r="V15" s="42" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AC15" s="8"/>
       <c r="AD15" s="8"/>
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.35">
       <c r="A16" s="32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="14">
         <v>13</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E16" s="14">
         <v>13</v>
       </c>
       <c r="F16" s="96" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="25"/>
@@ -7046,55 +7046,55 @@
         <v>8.1199999999999992</v>
       </c>
       <c r="K16" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L16" s="37"/>
       <c r="M16" s="70">
         <v>14</v>
       </c>
       <c r="N16" s="67" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O16" s="38"/>
       <c r="P16" s="46">
         <v>1.1299999999999999</v>
       </c>
       <c r="Q16" s="36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R16" s="35"/>
       <c r="S16" s="18"/>
       <c r="T16" s="18"/>
       <c r="U16" s="7"/>
       <c r="V16" s="42" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AC16" s="8"/>
       <c r="AD16" s="8"/>
     </row>
     <row r="17" spans="1:30" ht="25" x14ac:dyDescent="0.35">
       <c r="A17" s="32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="14">
         <v>14</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E17" s="14">
         <v>14</v>
       </c>
       <c r="F17" s="96" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="80">
         <v>2</v>
       </c>
       <c r="I17" s="81" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J17" s="14"/>
       <c r="K17" s="26"/>
@@ -7103,78 +7103,78 @@
         <v>15</v>
       </c>
       <c r="N17" s="67" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O17" s="38"/>
       <c r="P17" s="46">
         <v>1.1399999999999999</v>
       </c>
       <c r="Q17" s="36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R17" s="35"/>
       <c r="S17" s="18"/>
       <c r="T17" s="18"/>
       <c r="U17" s="7"/>
       <c r="V17" s="42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="X17" s="64" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="AC17" s="8"/>
       <c r="AD17" s="8"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A18" s="32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="14">
         <v>15</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E18" s="14">
         <v>15</v>
       </c>
       <c r="F18" s="96" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="25">
         <v>2.1</v>
       </c>
       <c r="I18" s="26" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J18" s="82">
         <v>9</v>
       </c>
       <c r="K18" s="81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L18" s="11"/>
       <c r="M18" s="70">
         <v>16</v>
       </c>
       <c r="N18" s="67" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O18" s="38"/>
       <c r="P18" s="46">
         <v>1.1499999999999999</v>
       </c>
       <c r="Q18" s="36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R18" s="35"/>
       <c r="S18" s="18"/>
       <c r="T18" s="18"/>
       <c r="U18" s="7"/>
       <c r="V18" s="43" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="X18" s="101" t="s">
         <v>2</v>
@@ -7184,54 +7184,54 @@
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A19" s="32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="14">
         <v>16</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E19" s="14">
         <v>16</v>
       </c>
       <c r="F19" s="96" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="25">
         <v>2.2000000000000002</v>
       </c>
       <c r="I19" s="26" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J19" s="14">
         <v>9.1</v>
       </c>
       <c r="K19" s="26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L19" s="37"/>
       <c r="M19" s="70">
         <v>17</v>
       </c>
       <c r="N19" s="67" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="O19" s="38"/>
       <c r="P19" s="46">
         <v>1.1599999999999999</v>
       </c>
       <c r="Q19" s="36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R19" s="35"/>
       <c r="S19" s="18"/>
       <c r="T19" s="18"/>
       <c r="U19" s="7"/>
       <c r="V19" s="42" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="X19" s="101" t="s">
         <v>4</v>
@@ -7245,45 +7245,45 @@
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A20" s="32" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="14">
         <v>17</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E20" s="14">
         <v>17</v>
       </c>
       <c r="F20" s="96" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="25">
         <v>2.2999999999999998</v>
       </c>
       <c r="I20" s="26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J20" s="14">
         <v>9.1999999999999993</v>
       </c>
       <c r="K20" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L20" s="37"/>
       <c r="M20" s="70">
         <v>18</v>
       </c>
       <c r="N20" s="67" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="O20" s="38"/>
       <c r="U20" s="7"/>
       <c r="V20" s="42" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="X20" s="101" t="s">
         <v>5</v>
@@ -7297,60 +7297,60 @@
     </row>
     <row r="21" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="14">
         <v>18</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E21" s="14">
         <v>18</v>
       </c>
       <c r="F21" s="96" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="25">
         <v>2.4</v>
       </c>
       <c r="I21" s="26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J21" s="14">
         <v>9.3000000000000007</v>
       </c>
       <c r="K21" s="26" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L21" s="37"/>
       <c r="M21" s="70">
         <v>19</v>
       </c>
       <c r="N21" s="67" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O21" s="38"/>
       <c r="P21" s="70">
         <v>2</v>
       </c>
       <c r="Q21" s="67" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R21" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S21" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S21" s="72" t="s">
+      <c r="T21" s="72" t="s">
         <v>436</v>
-      </c>
-      <c r="T21" s="72" t="s">
-        <v>437</v>
       </c>
       <c r="U21" s="7"/>
       <c r="V21" s="42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="X21" s="101" t="s">
         <v>6</v>
@@ -7364,47 +7364,47 @@
     </row>
     <row r="22" spans="1:30" ht="25" x14ac:dyDescent="0.35">
       <c r="A22" s="32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="14">
         <v>19</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E22" s="14">
         <v>19</v>
       </c>
       <c r="F22" s="96" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="25">
         <v>2.5</v>
       </c>
       <c r="I22" s="26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J22" s="14">
         <v>9.4</v>
       </c>
       <c r="K22" s="26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L22" s="37"/>
       <c r="M22" s="70">
         <v>20</v>
       </c>
       <c r="N22" s="67" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="O22" s="16"/>
       <c r="P22" s="46">
         <v>2.1</v>
       </c>
       <c r="Q22" s="36" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R22" s="34"/>
       <c r="S22" s="17"/>
@@ -7423,35 +7423,35 @@
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A23" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="14">
         <v>20</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E23" s="14">
         <v>20</v>
       </c>
       <c r="F23" s="96" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H23" s="25">
         <v>2.6</v>
       </c>
       <c r="I23" s="26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J23" s="14">
         <v>9.5</v>
       </c>
       <c r="K23" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L23" s="37"/>
       <c r="O23" s="16"/>
@@ -7459,7 +7459,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="Q23" s="36" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="R23" s="35"/>
       <c r="S23" s="18"/>
@@ -7478,47 +7478,47 @@
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A24" s="32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="14">
         <v>21</v>
       </c>
       <c r="D24" s="97" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E24" s="14">
         <v>21</v>
       </c>
       <c r="F24" s="96" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H24" s="25">
         <v>2.7</v>
       </c>
       <c r="I24" s="26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J24" s="14">
         <v>9.6</v>
       </c>
       <c r="K24" s="26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L24" s="37"/>
       <c r="M24" s="37"/>
       <c r="N24" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O24" s="16"/>
       <c r="P24" s="46">
         <v>2.2999999999999998</v>
       </c>
       <c r="Q24" s="36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="R24" s="35"/>
       <c r="S24" s="18"/>
@@ -7535,43 +7535,43 @@
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A25" s="32" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="14">
         <v>22</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E25" s="9"/>
       <c r="F25" s="10"/>
       <c r="G25" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H25" s="25">
         <v>2.8</v>
       </c>
       <c r="I25" s="26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J25" s="14">
         <v>9.6999999999999993</v>
       </c>
       <c r="K25" s="26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
       <c r="N25" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O25" s="16"/>
       <c r="P25" s="46">
         <v>2.4</v>
       </c>
       <c r="Q25" s="36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="R25" s="35"/>
       <c r="S25" s="18"/>
@@ -7579,7 +7579,7 @@
       <c r="U25" s="12"/>
       <c r="V25" s="15"/>
       <c r="X25" s="64" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="Y25" s="8"/>
       <c r="Z25" s="8"/>
@@ -7590,43 +7590,43 @@
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A26" s="32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="14">
         <v>23</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E26" s="9"/>
       <c r="F26" s="10"/>
       <c r="G26" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H26" s="25">
         <v>2.9</v>
       </c>
       <c r="I26" s="26" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J26" s="14">
         <v>9.8000000000000007</v>
       </c>
       <c r="K26" s="26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L26" s="37"/>
       <c r="M26" s="37"/>
       <c r="N26" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O26" s="16"/>
       <c r="P26" s="46">
         <v>2.5</v>
       </c>
       <c r="Q26" s="36" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R26" s="35"/>
       <c r="S26" s="18"/>
@@ -7634,7 +7634,7 @@
       <c r="U26" s="12"/>
       <c r="V26" s="15"/>
       <c r="X26" s="8" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="Y26" s="8"/>
       <c r="Z26" s="8"/>
@@ -7645,31 +7645,31 @@
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A27" s="32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F27" s="10"/>
       <c r="G27" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H27" s="27">
         <v>2.1</v>
       </c>
       <c r="I27" s="26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J27" s="14"/>
       <c r="K27" s="26"/>
       <c r="L27" s="37"/>
       <c r="M27" s="37"/>
       <c r="N27" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O27" s="16"/>
       <c r="P27" s="46">
         <v>2.6</v>
       </c>
       <c r="Q27" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R27" s="35"/>
       <c r="S27" s="18"/>
@@ -7677,37 +7677,37 @@
       <c r="U27" s="13"/>
       <c r="V27" s="15"/>
       <c r="X27" s="8" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.35">
       <c r="F28" s="10"/>
       <c r="G28" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H28" s="25">
         <v>2.11</v>
       </c>
       <c r="I28" s="26" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J28" s="82">
         <v>10</v>
       </c>
       <c r="K28" s="81" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L28" s="11"/>
       <c r="M28" s="11"/>
       <c r="N28" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O28" s="16"/>
       <c r="P28" s="46">
         <v>2.7</v>
       </c>
       <c r="Q28" s="36" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="R28" s="35"/>
       <c r="S28" s="18"/>
@@ -7716,7 +7716,7 @@
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.35">
       <c r="G29" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H29" s="25"/>
       <c r="I29" s="26"/>
@@ -7724,19 +7724,19 @@
         <v>10.1</v>
       </c>
       <c r="K29" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L29" s="37"/>
       <c r="M29" s="37"/>
       <c r="N29" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O29" s="16"/>
       <c r="P29" s="46">
         <v>2.8</v>
       </c>
       <c r="Q29" s="36" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="R29" s="35"/>
       <c r="S29" s="18"/>
@@ -7746,27 +7746,27 @@
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A30" s="62" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H30" s="80">
         <v>3</v>
       </c>
       <c r="I30" s="81" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J30" s="14">
         <v>10.199999999999999</v>
       </c>
       <c r="K30" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L30" s="37"/>
       <c r="M30" s="37"/>
       <c r="N30" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O30" s="16"/>
       <c r="T30" s="40"/>
@@ -7775,77 +7775,77 @@
     </row>
     <row r="31" spans="1:30" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="33" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H31" s="25">
         <v>3.1</v>
       </c>
       <c r="I31" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J31" s="14">
         <v>10.3</v>
       </c>
       <c r="K31" s="26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L31" s="37"/>
       <c r="M31" s="37"/>
       <c r="N31" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O31" s="16"/>
       <c r="P31" s="70">
         <v>3</v>
       </c>
       <c r="Q31" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R31" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S31" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S31" s="72" t="s">
+      <c r="T31" s="72" t="s">
         <v>436</v>
-      </c>
-      <c r="T31" s="72" t="s">
-        <v>437</v>
       </c>
       <c r="U31" s="13"/>
       <c r="V31" s="100"/>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A32" s="33" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H32" s="25">
         <v>3.2</v>
       </c>
       <c r="I32" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J32" s="14">
         <v>10.4</v>
       </c>
       <c r="K32" s="26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L32" s="37"/>
       <c r="M32" s="37"/>
       <c r="N32" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O32" s="16"/>
       <c r="P32" s="46">
         <v>3.1</v>
       </c>
       <c r="Q32" s="36" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="R32" s="18"/>
       <c r="S32" s="18"/>
@@ -7855,34 +7855,34 @@
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A33" s="33" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H33" s="25">
         <v>3.3</v>
       </c>
       <c r="I33" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J33" s="14">
         <v>10.5</v>
       </c>
       <c r="K33" s="26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L33" s="37"/>
       <c r="M33" s="37"/>
       <c r="N33" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O33" s="16"/>
       <c r="P33" s="46">
         <v>3.2</v>
       </c>
       <c r="Q33" s="36" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R33" s="18"/>
       <c r="S33" s="18"/>
@@ -7892,34 +7892,34 @@
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A34" s="33" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H34" s="25">
         <v>3.4</v>
       </c>
       <c r="I34" s="26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J34" s="14">
         <v>10.6</v>
       </c>
       <c r="K34" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
       <c r="N34" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O34" s="16"/>
       <c r="P34" s="46">
         <v>3.3</v>
       </c>
       <c r="Q34" s="36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R34" s="18"/>
       <c r="S34" s="18"/>
@@ -7929,31 +7929,31 @@
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
       <c r="G35" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H35" s="25">
         <v>3.5</v>
       </c>
       <c r="I35" s="26" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J35" s="14">
         <v>10.7</v>
       </c>
       <c r="K35" s="26" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L35" s="37"/>
       <c r="M35" s="37"/>
       <c r="N35" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O35" s="16"/>
       <c r="P35" s="46">
         <v>3.4</v>
       </c>
       <c r="Q35" s="36" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R35" s="18"/>
       <c r="S35" s="18"/>
@@ -7963,31 +7963,31 @@
     </row>
     <row r="36" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G36" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H36" s="25">
         <v>3.6</v>
       </c>
       <c r="I36" s="26" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J36" s="14">
         <v>10.8</v>
       </c>
       <c r="K36" s="26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L36" s="37"/>
       <c r="M36" s="37"/>
       <c r="N36" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O36" s="16"/>
       <c r="P36" s="46">
         <v>3.5</v>
       </c>
       <c r="Q36" s="36" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R36" s="18"/>
       <c r="S36" s="18"/>
@@ -7997,31 +7997,31 @@
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
       <c r="G37" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H37" s="25">
         <v>3.7</v>
       </c>
       <c r="I37" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J37" s="14">
         <v>10.9</v>
       </c>
       <c r="K37" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L37" s="37"/>
       <c r="M37" s="37"/>
       <c r="N37" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O37" s="16"/>
       <c r="P37" s="46">
         <v>3.6</v>
       </c>
       <c r="Q37" s="36" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="R37" s="18"/>
       <c r="S37" s="18"/>
@@ -8031,31 +8031,31 @@
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.35">
       <c r="G38" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H38" s="25">
         <v>3.8</v>
       </c>
       <c r="I38" s="26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J38" s="28">
         <v>10.1</v>
       </c>
       <c r="K38" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L38" s="37"/>
       <c r="M38" s="37"/>
       <c r="N38" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O38" s="16"/>
       <c r="P38" s="46">
         <v>3.7</v>
       </c>
       <c r="Q38" s="36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R38" s="18"/>
       <c r="S38" s="18"/>
@@ -8065,31 +8065,31 @@
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.35">
       <c r="G39" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H39" s="25">
         <v>3.9</v>
       </c>
       <c r="I39" s="26" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J39" s="14">
         <v>10.11</v>
       </c>
       <c r="K39" s="26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L39" s="37"/>
       <c r="M39" s="37"/>
       <c r="N39" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O39" s="16"/>
       <c r="P39" s="46">
         <v>3.8</v>
       </c>
       <c r="Q39" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="R39" s="18"/>
       <c r="S39" s="18"/>
@@ -8099,31 +8099,31 @@
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
       <c r="G40" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H40" s="27">
         <v>3.1</v>
       </c>
       <c r="I40" s="26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J40" s="14">
         <v>10.119999999999999</v>
       </c>
       <c r="K40" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L40" s="37"/>
       <c r="M40" s="37"/>
       <c r="N40" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O40" s="16"/>
       <c r="P40" s="46">
         <v>3.9</v>
       </c>
       <c r="Q40" s="36" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R40" s="18"/>
       <c r="S40" s="18"/>
@@ -8133,20 +8133,20 @@
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
       <c r="G41" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H41" s="25">
         <v>3.11</v>
       </c>
       <c r="I41" s="26" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J41" s="14"/>
       <c r="K41" s="26"/>
       <c r="L41" s="37"/>
       <c r="M41" s="37"/>
       <c r="N41" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O41" s="16"/>
       <c r="U41" s="13"/>
@@ -8154,7 +8154,7 @@
     </row>
     <row r="42" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G42" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H42" s="25"/>
       <c r="I42" s="26"/>
@@ -8162,59 +8162,59 @@
         <v>11</v>
       </c>
       <c r="K42" s="81" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L42" s="11"/>
       <c r="M42" s="11"/>
       <c r="N42" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O42" s="16"/>
       <c r="P42" s="70">
         <v>4</v>
       </c>
       <c r="Q42" s="67" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R42" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S42" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S42" s="72" t="s">
+      <c r="T42" s="72" t="s">
         <v>436</v>
-      </c>
-      <c r="T42" s="72" t="s">
-        <v>437</v>
       </c>
       <c r="U42" s="13"/>
       <c r="V42" s="100"/>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
       <c r="G43" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H43" s="80">
         <v>4</v>
       </c>
       <c r="I43" s="81" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J43" s="83">
         <v>11.1</v>
       </c>
       <c r="K43" s="84" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L43" s="37"/>
       <c r="M43" s="37"/>
       <c r="N43" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O43" s="16"/>
       <c r="P43" s="46">
         <v>4.0999999999999996</v>
       </c>
       <c r="Q43" s="36" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="R43" s="34"/>
       <c r="S43" s="17"/>
@@ -8224,31 +8224,31 @@
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
       <c r="G44" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H44" s="25">
         <v>4.0999999999999996</v>
       </c>
       <c r="I44" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="J44" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="J44" s="14" t="s">
+      <c r="K44" s="26" t="s">
         <v>169</v>
-      </c>
-      <c r="K44" s="26" t="s">
-        <v>170</v>
       </c>
       <c r="L44" s="37"/>
       <c r="M44" s="37"/>
       <c r="N44" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O44" s="16"/>
       <c r="P44" s="46">
         <v>4.2</v>
       </c>
       <c r="Q44" s="36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="R44" s="35"/>
       <c r="S44" s="18"/>
@@ -8258,31 +8258,31 @@
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
       <c r="G45" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H45" s="25">
         <v>4.2</v>
       </c>
       <c r="I45" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="J45" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="J45" s="14" t="s">
+      <c r="K45" s="26" t="s">
         <v>173</v>
-      </c>
-      <c r="K45" s="26" t="s">
-        <v>174</v>
       </c>
       <c r="L45" s="37"/>
       <c r="M45" s="37"/>
       <c r="N45" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O45" s="16"/>
       <c r="P45" s="46">
         <v>4.3</v>
       </c>
       <c r="Q45" s="36" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="R45" s="35"/>
       <c r="S45" s="18"/>
@@ -8292,31 +8292,31 @@
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
       <c r="G46" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H46" s="25">
         <v>4.3</v>
       </c>
       <c r="I46" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="J46" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="J46" s="14" t="s">
+      <c r="K46" s="26" t="s">
         <v>177</v>
-      </c>
-      <c r="K46" s="26" t="s">
-        <v>178</v>
       </c>
       <c r="L46" s="37"/>
       <c r="M46" s="37"/>
       <c r="N46" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O46" s="16"/>
       <c r="P46" s="46">
         <v>4.4000000000000004</v>
       </c>
       <c r="Q46" s="36" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R46" s="35"/>
       <c r="S46" s="18"/>
@@ -8326,31 +8326,31 @@
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
       <c r="G47" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H47" s="25">
         <v>4.4000000000000004</v>
       </c>
       <c r="I47" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="J47" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="J47" s="14" t="s">
+      <c r="K47" s="26" t="s">
         <v>181</v>
-      </c>
-      <c r="K47" s="26" t="s">
-        <v>182</v>
       </c>
       <c r="L47" s="37"/>
       <c r="M47" s="37"/>
       <c r="N47" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O47" s="16"/>
       <c r="P47" s="46">
         <v>4.5</v>
       </c>
       <c r="Q47" s="36" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="R47" s="35"/>
       <c r="S47" s="18"/>
@@ -8360,94 +8360,94 @@
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
       <c r="G48" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H48" s="25">
         <v>4.5</v>
       </c>
       <c r="I48" s="26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J48" s="83">
         <v>11.2</v>
       </c>
       <c r="K48" s="84" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L48" s="37"/>
       <c r="M48" s="37"/>
       <c r="N48" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O48" s="16"/>
       <c r="U48" s="13"/>
     </row>
     <row r="49" spans="7:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G49" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H49" s="25">
         <v>4.7</v>
       </c>
       <c r="I49" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="J49" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="J49" s="14" t="s">
+      <c r="K49" s="26" t="s">
         <v>188</v>
-      </c>
-      <c r="K49" s="26" t="s">
-        <v>189</v>
       </c>
       <c r="L49" s="37"/>
       <c r="M49" s="37"/>
       <c r="N49" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O49" s="16"/>
       <c r="P49" s="70">
         <v>5</v>
       </c>
       <c r="Q49" s="67" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="R49" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S49" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S49" s="72" t="s">
+      <c r="T49" s="72" t="s">
         <v>436</v>
-      </c>
-      <c r="T49" s="72" t="s">
-        <v>437</v>
       </c>
       <c r="U49" s="13"/>
     </row>
     <row r="50" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G50" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H50" s="25">
         <v>4.8</v>
       </c>
       <c r="I50" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="J50" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="J50" s="14" t="s">
+      <c r="K50" s="26" t="s">
         <v>192</v>
-      </c>
-      <c r="K50" s="26" t="s">
-        <v>193</v>
       </c>
       <c r="L50" s="37"/>
       <c r="M50" s="37"/>
       <c r="N50" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O50" s="16"/>
       <c r="P50" s="46">
         <v>5.0999999999999996</v>
       </c>
       <c r="Q50" s="36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R50" s="18"/>
       <c r="S50" s="18"/>
@@ -8456,31 +8456,31 @@
     </row>
     <row r="51" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G51" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H51" s="25">
         <v>4.9000000000000004</v>
       </c>
       <c r="I51" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="J51" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="J51" s="14" t="s">
+      <c r="K51" s="26" t="s">
         <v>196</v>
-      </c>
-      <c r="K51" s="26" t="s">
-        <v>197</v>
       </c>
       <c r="L51" s="37"/>
       <c r="M51" s="37"/>
       <c r="N51" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O51" s="16"/>
       <c r="P51" s="46">
         <v>5.2</v>
       </c>
       <c r="Q51" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R51" s="18"/>
       <c r="S51" s="18"/>
@@ -8489,27 +8489,27 @@
     </row>
     <row r="52" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G52" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H52" s="27">
         <v>4.0999999999999996</v>
       </c>
       <c r="I52" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J52" s="14"/>
       <c r="K52" s="26"/>
       <c r="L52" s="37"/>
       <c r="M52" s="37"/>
       <c r="N52" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O52" s="16"/>
       <c r="P52" s="46">
         <v>5.3</v>
       </c>
       <c r="Q52" s="36" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="R52" s="18"/>
       <c r="S52" s="18"/>
@@ -8518,31 +8518,31 @@
     </row>
     <row r="53" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G53" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H53" s="25">
         <v>4.1100000000000003</v>
       </c>
       <c r="I53" s="26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J53" s="82">
         <v>12</v>
       </c>
       <c r="K53" s="81" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L53" s="11"/>
       <c r="M53" s="11"/>
       <c r="N53" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O53" s="16"/>
       <c r="P53" s="46">
         <v>5.4</v>
       </c>
       <c r="Q53" s="36" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="R53" s="18"/>
       <c r="S53" s="18"/>
@@ -8551,7 +8551,7 @@
     </row>
     <row r="54" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G54" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H54" s="25"/>
       <c r="I54" s="26"/>
@@ -8559,19 +8559,19 @@
         <v>12.1</v>
       </c>
       <c r="K54" s="26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L54" s="37"/>
       <c r="M54" s="37"/>
       <c r="N54" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O54" s="16"/>
       <c r="P54" s="46">
         <v>5.5</v>
       </c>
       <c r="Q54" s="36" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="R54" s="18"/>
       <c r="S54" s="18"/>
@@ -8580,24 +8580,24 @@
     </row>
     <row r="55" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G55" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H55" s="80">
         <v>5</v>
       </c>
       <c r="I55" s="81" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J55" s="14">
         <v>12.2</v>
       </c>
       <c r="K55" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L55" s="37"/>
       <c r="M55" s="37"/>
       <c r="N55" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O55" s="16"/>
       <c r="P55" s="16"/>
@@ -8609,70 +8609,70 @@
     </row>
     <row r="56" spans="7:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G56" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H56" s="25">
         <v>5.0999999999999996</v>
       </c>
       <c r="I56" s="26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J56" s="14">
         <v>12.3</v>
       </c>
       <c r="K56" s="26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L56" s="37"/>
       <c r="M56" s="37"/>
       <c r="N56" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O56" s="16"/>
       <c r="P56" s="70">
         <v>6</v>
       </c>
       <c r="Q56" s="67" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="R56" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S56" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S56" s="72" t="s">
+      <c r="T56" s="72" t="s">
         <v>436</v>
-      </c>
-      <c r="T56" s="72" t="s">
-        <v>437</v>
       </c>
       <c r="U56" s="13"/>
     </row>
     <row r="57" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G57" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H57" s="25">
         <v>5.2</v>
       </c>
       <c r="I57" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J57" s="14">
         <v>12.4</v>
       </c>
       <c r="K57" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L57" s="37"/>
       <c r="M57" s="37"/>
       <c r="N57" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O57" s="16"/>
       <c r="P57" s="46">
         <v>6.1</v>
       </c>
       <c r="Q57" s="36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R57" s="18"/>
       <c r="S57" s="18"/>
@@ -8681,31 +8681,31 @@
     </row>
     <row r="58" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G58" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H58" s="25">
         <v>5.3</v>
       </c>
       <c r="I58" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J58" s="14">
         <v>12.5</v>
       </c>
       <c r="K58" s="26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L58" s="37"/>
       <c r="M58" s="37"/>
       <c r="N58" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O58" s="16"/>
       <c r="P58" s="46">
         <v>6.2</v>
       </c>
       <c r="Q58" s="36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="R58" s="18"/>
       <c r="S58" s="18"/>
@@ -8714,31 +8714,31 @@
     </row>
     <row r="59" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G59" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H59" s="25">
         <v>5.4</v>
       </c>
       <c r="I59" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J59" s="14">
         <v>12.6</v>
       </c>
       <c r="K59" s="26" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L59" s="37"/>
       <c r="M59" s="37"/>
       <c r="N59" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O59" s="16"/>
       <c r="P59" s="46">
         <v>6.3</v>
       </c>
       <c r="Q59" s="36" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R59" s="18"/>
       <c r="S59" s="18"/>
@@ -8747,31 +8747,31 @@
     </row>
     <row r="60" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G60" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H60" s="25">
         <v>5.5</v>
       </c>
       <c r="I60" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J60" s="14">
         <v>12.7</v>
       </c>
       <c r="K60" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="L60" s="37"/>
       <c r="M60" s="37"/>
       <c r="N60" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O60" s="16"/>
       <c r="P60" s="46">
         <v>6.4</v>
       </c>
       <c r="Q60" s="36" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R60" s="18"/>
       <c r="S60" s="18"/>
@@ -8780,7 +8780,7 @@
     </row>
     <row r="61" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G61" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H61" s="25"/>
       <c r="I61" s="26"/>
@@ -8789,14 +8789,14 @@
       <c r="L61" s="37"/>
       <c r="M61" s="37"/>
       <c r="N61" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O61" s="16"/>
       <c r="P61" s="46">
         <v>6.5</v>
       </c>
       <c r="Q61" s="36" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="R61" s="18"/>
       <c r="S61" s="18"/>
@@ -8805,31 +8805,31 @@
     </row>
     <row r="62" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G62" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H62" s="80">
         <v>6</v>
       </c>
       <c r="I62" s="81" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J62" s="82">
         <v>13</v>
       </c>
       <c r="K62" s="81" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L62" s="11"/>
       <c r="M62" s="11"/>
       <c r="N62" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O62" s="16"/>
       <c r="P62" s="46">
         <v>6.6</v>
       </c>
       <c r="Q62" s="36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="R62" s="18"/>
       <c r="S62" s="18"/>
@@ -8838,109 +8838,109 @@
     </row>
     <row r="63" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G63" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H63" s="25">
         <v>6.1</v>
       </c>
       <c r="I63" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J63" s="83">
         <v>13.1</v>
       </c>
       <c r="K63" s="84" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L63" s="37"/>
       <c r="M63" s="37"/>
       <c r="N63" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O63" s="16"/>
       <c r="P63" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q63" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R63" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S63" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T63" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U63" s="13"/>
     </row>
     <row r="64" spans="7:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G64" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H64" s="25">
         <v>6.2</v>
       </c>
       <c r="I64" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="J64" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="J64" s="14" t="s">
+      <c r="K64" s="26" t="s">
         <v>229</v>
-      </c>
-      <c r="K64" s="26" t="s">
-        <v>230</v>
       </c>
       <c r="L64" s="37"/>
       <c r="M64" s="37"/>
       <c r="N64" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O64" s="16"/>
       <c r="P64" s="70">
         <v>7</v>
       </c>
       <c r="Q64" s="67" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R64" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S64" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S64" s="72" t="s">
+      <c r="T64" s="72" t="s">
         <v>436</v>
-      </c>
-      <c r="T64" s="72" t="s">
-        <v>437</v>
       </c>
       <c r="U64" s="13"/>
     </row>
     <row r="65" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G65" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H65" s="25">
         <v>6.3</v>
       </c>
       <c r="I65" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="J65" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="J65" s="14" t="s">
+      <c r="K65" s="26" t="s">
         <v>232</v>
-      </c>
-      <c r="K65" s="26" t="s">
-        <v>233</v>
       </c>
       <c r="L65" s="37"/>
       <c r="M65" s="37"/>
       <c r="N65" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O65" s="16"/>
       <c r="P65" s="46">
         <v>7.1</v>
       </c>
       <c r="Q65" s="36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R65" s="18"/>
       <c r="S65" s="18"/>
@@ -8949,31 +8949,31 @@
     </row>
     <row r="66" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G66" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H66" s="25">
         <v>6.4</v>
       </c>
       <c r="I66" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="J66" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="J66" s="14" t="s">
+      <c r="K66" s="26" t="s">
         <v>236</v>
-      </c>
-      <c r="K66" s="26" t="s">
-        <v>237</v>
       </c>
       <c r="L66" s="37"/>
       <c r="M66" s="37"/>
       <c r="N66" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O66" s="16"/>
       <c r="P66" s="46">
         <v>7.2</v>
       </c>
       <c r="Q66" s="36" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="R66" s="18"/>
       <c r="S66" s="18"/>
@@ -8982,31 +8982,31 @@
     </row>
     <row r="67" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G67" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H67" s="25">
         <v>6.5</v>
       </c>
       <c r="I67" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="J67" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="J67" s="14" t="s">
+      <c r="K67" s="26" t="s">
         <v>239</v>
-      </c>
-      <c r="K67" s="26" t="s">
-        <v>240</v>
       </c>
       <c r="L67" s="37"/>
       <c r="M67" s="37"/>
       <c r="N67" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O67" s="16"/>
       <c r="P67" s="46">
         <v>7.3</v>
       </c>
       <c r="Q67" s="36" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="R67" s="18"/>
       <c r="S67" s="18"/>
@@ -9015,7 +9015,7 @@
     </row>
     <row r="68" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G68" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H68" s="25"/>
       <c r="I68" s="26"/>
@@ -9023,19 +9023,19 @@
         <v>13.2</v>
       </c>
       <c r="K68" s="84" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L68" s="37"/>
       <c r="M68" s="37"/>
       <c r="N68" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O68" s="16"/>
       <c r="P68" s="46">
         <v>7.4</v>
       </c>
       <c r="Q68" s="36" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="R68" s="18"/>
       <c r="S68" s="18"/>
@@ -9044,31 +9044,31 @@
     </row>
     <row r="69" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G69" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H69" s="80">
         <v>7</v>
       </c>
       <c r="I69" s="81" t="s">
+        <v>242</v>
+      </c>
+      <c r="J69" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="J69" s="14" t="s">
+      <c r="K69" s="26" t="s">
         <v>244</v>
-      </c>
-      <c r="K69" s="26" t="s">
-        <v>245</v>
       </c>
       <c r="L69" s="37"/>
       <c r="M69" s="37"/>
       <c r="N69" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O69" s="16"/>
       <c r="P69" s="46">
         <v>7.5</v>
       </c>
       <c r="Q69" s="36" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R69" s="18"/>
       <c r="S69" s="18"/>
@@ -9077,31 +9077,31 @@
     </row>
     <row r="70" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G70" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H70" s="25">
         <v>7.1</v>
       </c>
       <c r="I70" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="J70" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="J70" s="14" t="s">
+      <c r="K70" s="26" t="s">
         <v>248</v>
-      </c>
-      <c r="K70" s="26" t="s">
-        <v>249</v>
       </c>
       <c r="L70" s="37"/>
       <c r="M70" s="37"/>
       <c r="N70" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O70" s="16"/>
       <c r="P70" s="46">
         <v>7.6</v>
       </c>
       <c r="Q70" s="36" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R70" s="18"/>
       <c r="S70" s="18"/>
@@ -9110,31 +9110,31 @@
     </row>
     <row r="71" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G71" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H71" s="25">
         <v>7.2</v>
       </c>
       <c r="I71" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="J71" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="J71" s="14" t="s">
+      <c r="K71" s="26" t="s">
         <v>252</v>
-      </c>
-      <c r="K71" s="26" t="s">
-        <v>253</v>
       </c>
       <c r="L71" s="37"/>
       <c r="M71" s="37"/>
       <c r="N71" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O71" s="16"/>
       <c r="P71" s="46">
         <v>7.7</v>
       </c>
       <c r="Q71" s="36" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="R71" s="18"/>
       <c r="S71" s="18"/>
@@ -9143,31 +9143,31 @@
     </row>
     <row r="72" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G72" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H72" s="25">
         <v>7.3</v>
       </c>
       <c r="I72" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="J72" s="14" t="s">
         <v>255</v>
       </c>
-      <c r="J72" s="14" t="s">
+      <c r="K72" s="26" t="s">
         <v>256</v>
-      </c>
-      <c r="K72" s="26" t="s">
-        <v>257</v>
       </c>
       <c r="L72" s="37"/>
       <c r="M72" s="37"/>
       <c r="N72" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O72" s="16"/>
       <c r="P72" s="46">
         <v>7.8</v>
       </c>
       <c r="Q72" s="36" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="R72" s="18"/>
       <c r="S72" s="18"/>
@@ -9176,31 +9176,31 @@
     </row>
     <row r="73" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G73" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H73" s="25">
         <v>7.4</v>
       </c>
       <c r="I73" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="J73" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="J73" s="14" t="s">
-        <v>260</v>
-      </c>
       <c r="K73" s="26" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L73" s="37"/>
       <c r="M73" s="37"/>
       <c r="N73" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O73" s="16"/>
       <c r="P73" s="46">
         <v>7.9</v>
       </c>
       <c r="Q73" s="36" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="R73" s="18"/>
       <c r="S73" s="18"/>
@@ -9208,31 +9208,31 @@
     </row>
     <row r="74" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G74" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H74" s="25">
         <v>7.5</v>
       </c>
       <c r="I74" s="26" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J74" s="83">
         <v>13.3</v>
       </c>
       <c r="K74" s="84" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
       <c r="N74" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O74" s="16"/>
       <c r="P74" s="87">
         <v>7.1</v>
       </c>
       <c r="Q74" s="36" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="R74" s="18"/>
       <c r="S74" s="18"/>
@@ -9241,31 +9241,31 @@
     </row>
     <row r="75" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G75" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H75" s="25">
         <v>7.6</v>
       </c>
       <c r="I75" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="J75" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="J75" s="14" t="s">
+      <c r="K75" s="26" t="s">
         <v>266</v>
-      </c>
-      <c r="K75" s="26" t="s">
-        <v>267</v>
       </c>
       <c r="L75" s="37"/>
       <c r="M75" s="37"/>
       <c r="N75" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O75" s="16"/>
       <c r="P75" s="46">
         <v>7.11</v>
       </c>
       <c r="Q75" s="36" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="R75" s="18"/>
       <c r="S75" s="18"/>
@@ -9274,31 +9274,31 @@
     </row>
     <row r="76" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G76" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H76" s="25">
         <v>7.7</v>
       </c>
       <c r="I76" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="J76" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="J76" s="14" t="s">
+      <c r="K76" s="26" t="s">
         <v>270</v>
-      </c>
-      <c r="K76" s="26" t="s">
-        <v>271</v>
       </c>
       <c r="L76" s="37"/>
       <c r="M76" s="37"/>
       <c r="N76" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O76" s="16"/>
       <c r="P76" s="46">
         <v>7.12</v>
       </c>
       <c r="Q76" s="36" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R76" s="18"/>
       <c r="S76" s="18"/>
@@ -9307,31 +9307,31 @@
     </row>
     <row r="77" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G77" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H77" s="25">
         <v>7.8</v>
       </c>
       <c r="I77" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="J77" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="J77" s="14" t="s">
+      <c r="K77" s="26" t="s">
         <v>274</v>
-      </c>
-      <c r="K77" s="26" t="s">
-        <v>275</v>
       </c>
       <c r="L77" s="37"/>
       <c r="M77" s="37"/>
       <c r="N77" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O77" s="16"/>
       <c r="P77" s="46">
         <v>7.13</v>
       </c>
       <c r="Q77" s="36" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="R77" s="18"/>
       <c r="S77" s="18"/>
@@ -9340,92 +9340,92 @@
     </row>
     <row r="78" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G78" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H78" s="25">
         <v>7.9</v>
       </c>
       <c r="I78" s="26" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J78" s="14"/>
       <c r="K78" s="26"/>
       <c r="L78" s="37"/>
       <c r="M78" s="37"/>
       <c r="N78" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O78" s="16"/>
       <c r="U78" s="13"/>
     </row>
     <row r="79" spans="7:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G79" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H79" s="27">
         <v>7.1</v>
       </c>
       <c r="I79" s="26" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J79" s="82">
         <v>14</v>
       </c>
       <c r="K79" s="81" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L79" s="11"/>
       <c r="M79" s="11"/>
       <c r="N79" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O79" s="16"/>
       <c r="P79" s="70">
         <v>8</v>
       </c>
       <c r="Q79" s="67" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="R79" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S79" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S79" s="72" t="s">
+      <c r="T79" s="72" t="s">
         <v>436</v>
       </c>
-      <c r="T79" s="72" t="s">
-        <v>437</v>
-      </c>
       <c r="U79" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G80" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H80" s="25">
         <v>7.11</v>
       </c>
       <c r="I80" s="26" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J80" s="14">
         <v>14.1</v>
       </c>
       <c r="K80" s="26" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L80" s="37"/>
       <c r="M80" s="37"/>
       <c r="N80" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O80" s="16"/>
       <c r="P80" s="46">
         <v>8.1</v>
       </c>
       <c r="Q80" s="36" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="R80" s="18"/>
       <c r="S80" s="18"/>
@@ -9434,31 +9434,31 @@
     </row>
     <row r="81" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G81" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H81" s="25">
         <v>7.12</v>
       </c>
       <c r="I81" s="26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J81" s="14">
         <v>14.2</v>
       </c>
       <c r="K81" s="26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L81" s="37"/>
       <c r="M81" s="37"/>
       <c r="N81" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O81" s="16"/>
       <c r="P81" s="46">
         <v>8.1999999999999993</v>
       </c>
       <c r="Q81" s="36" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="R81" s="18"/>
       <c r="S81" s="18"/>
@@ -9467,31 +9467,31 @@
     </row>
     <row r="82" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G82" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H82" s="25">
         <v>7.13</v>
       </c>
       <c r="I82" s="26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J82" s="14">
         <v>14.3</v>
       </c>
       <c r="K82" s="26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L82" s="37"/>
       <c r="M82" s="37"/>
       <c r="N82" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O82" s="16"/>
       <c r="P82" s="46">
         <v>8.3000000000000007</v>
       </c>
       <c r="Q82" s="36" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="R82" s="18"/>
       <c r="S82" s="18"/>
@@ -9500,31 +9500,31 @@
     </row>
     <row r="83" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G83" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H83" s="25">
         <v>7.14</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J83" s="14">
         <v>14.4</v>
       </c>
       <c r="K83" s="26" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L83" s="37"/>
       <c r="M83" s="37"/>
       <c r="N83" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O83" s="16"/>
       <c r="P83" s="46">
         <v>8.4</v>
       </c>
       <c r="Q83" s="36" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="R83" s="18"/>
       <c r="S83" s="18"/>
@@ -9533,7 +9533,7 @@
     </row>
     <row r="84" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G84" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H84" s="55"/>
       <c r="I84" s="85"/>
@@ -9541,19 +9541,19 @@
         <v>14.5</v>
       </c>
       <c r="K84" s="26" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="L84" s="37"/>
       <c r="M84" s="37"/>
       <c r="N84" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O84" s="16"/>
       <c r="P84" s="46">
         <v>8.5</v>
       </c>
       <c r="Q84" s="36" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="R84" s="18"/>
       <c r="S84" s="18"/>
@@ -9562,7 +9562,7 @@
     </row>
     <row r="85" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G85" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H85" s="9"/>
       <c r="I85" s="86"/>
@@ -9570,19 +9570,19 @@
         <v>14.6</v>
       </c>
       <c r="K85" s="26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="L85" s="37"/>
       <c r="M85" s="37"/>
       <c r="N85" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O85" s="16"/>
       <c r="P85" s="46">
         <v>8.6</v>
       </c>
       <c r="Q85" s="36" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="R85" s="18"/>
       <c r="S85" s="18"/>
@@ -9591,7 +9591,7 @@
     </row>
     <row r="86" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G86" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H86" s="9"/>
       <c r="I86" s="86"/>
@@ -9599,19 +9599,19 @@
         <v>14.7</v>
       </c>
       <c r="K86" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L86" s="37"/>
       <c r="M86" s="37"/>
       <c r="N86" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O86" s="16"/>
       <c r="P86" s="46">
         <v>8.6999999999999993</v>
       </c>
       <c r="Q86" s="36" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R86" s="18"/>
       <c r="S86" s="18"/>
@@ -9620,7 +9620,7 @@
     </row>
     <row r="87" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G87" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H87" s="9"/>
       <c r="I87" s="86"/>
@@ -9629,14 +9629,14 @@
       <c r="L87" s="37"/>
       <c r="M87" s="37"/>
       <c r="N87" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O87" s="16"/>
       <c r="U87" s="13"/>
     </row>
     <row r="88" spans="7:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G88" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H88" s="9"/>
       <c r="I88" s="86"/>
@@ -9644,34 +9644,34 @@
         <v>15</v>
       </c>
       <c r="K88" s="81" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L88" s="11"/>
       <c r="M88" s="11"/>
       <c r="N88" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O88" s="16"/>
       <c r="P88" s="70">
         <v>9</v>
       </c>
       <c r="Q88" s="67" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="R88" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S88" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S88" s="72" t="s">
+      <c r="T88" s="72" t="s">
         <v>436</v>
-      </c>
-      <c r="T88" s="72" t="s">
-        <v>437</v>
       </c>
       <c r="U88" s="13"/>
     </row>
     <row r="89" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G89" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H89" s="9"/>
       <c r="I89" s="86"/>
@@ -9679,19 +9679,19 @@
         <v>15.1</v>
       </c>
       <c r="K89" s="84" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L89" s="37"/>
       <c r="M89" s="37"/>
       <c r="N89" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O89" s="16"/>
       <c r="P89" s="46">
         <v>9.1</v>
       </c>
       <c r="Q89" s="36" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="R89" s="18"/>
       <c r="S89" s="18"/>
@@ -9700,27 +9700,27 @@
     </row>
     <row r="90" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G90" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H90" s="9"/>
       <c r="I90" s="86"/>
       <c r="J90" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="K90" s="26" t="s">
         <v>303</v>
-      </c>
-      <c r="K90" s="26" t="s">
-        <v>304</v>
       </c>
       <c r="L90" s="37"/>
       <c r="M90" s="37"/>
       <c r="N90" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O90" s="16"/>
       <c r="P90" s="46">
         <v>9.1999999999999993</v>
       </c>
       <c r="Q90" s="36" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="R90" s="18"/>
       <c r="S90" s="18"/>
@@ -9729,27 +9729,27 @@
     </row>
     <row r="91" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G91" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H91" s="9"/>
       <c r="I91" s="86"/>
       <c r="J91" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="K91" s="26" t="s">
         <v>306</v>
-      </c>
-      <c r="K91" s="26" t="s">
-        <v>307</v>
       </c>
       <c r="L91" s="37"/>
       <c r="M91" s="37"/>
       <c r="N91" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O91" s="16"/>
       <c r="P91" s="46">
         <v>9.3000000000000007</v>
       </c>
       <c r="Q91" s="36" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="R91" s="18"/>
       <c r="S91" s="18"/>
@@ -9758,7 +9758,7 @@
     </row>
     <row r="92" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G92" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H92" s="9"/>
       <c r="I92" s="86"/>
@@ -9766,19 +9766,19 @@
         <v>15.2</v>
       </c>
       <c r="K92" s="84" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L92" s="37"/>
       <c r="M92" s="37"/>
       <c r="N92" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O92" s="16"/>
       <c r="P92" s="46">
         <v>9.4</v>
       </c>
       <c r="Q92" s="36" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="R92" s="18"/>
       <c r="S92" s="18"/>
@@ -9787,27 +9787,27 @@
     </row>
     <row r="93" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G93" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H93" s="9"/>
       <c r="I93" s="86"/>
       <c r="J93" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="K93" s="26" t="s">
         <v>311</v>
-      </c>
-      <c r="K93" s="26" t="s">
-        <v>312</v>
       </c>
       <c r="L93" s="37"/>
       <c r="M93" s="37"/>
       <c r="N93" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O93" s="16"/>
       <c r="P93" s="46">
         <v>9.5</v>
       </c>
       <c r="Q93" s="36" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="R93" s="18"/>
       <c r="S93" s="18"/>
@@ -9816,27 +9816,27 @@
     </row>
     <row r="94" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G94" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H94" s="9"/>
       <c r="I94" s="86"/>
       <c r="J94" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="K94" s="26" t="s">
         <v>314</v>
-      </c>
-      <c r="K94" s="26" t="s">
-        <v>315</v>
       </c>
       <c r="L94" s="37"/>
       <c r="M94" s="37"/>
       <c r="N94" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O94" s="16"/>
       <c r="U94" s="13"/>
     </row>
     <row r="95" spans="7:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G95" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H95" s="16"/>
       <c r="I95" s="11"/>
@@ -9845,29 +9845,29 @@
       <c r="L95" s="11"/>
       <c r="M95" s="11"/>
       <c r="N95" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O95" s="16"/>
       <c r="P95" s="70">
         <v>10</v>
       </c>
       <c r="Q95" s="67" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="R95" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S95" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S95" s="72" t="s">
+      <c r="T95" s="72" t="s">
         <v>436</v>
-      </c>
-      <c r="T95" s="72" t="s">
-        <v>437</v>
       </c>
       <c r="U95" s="13"/>
     </row>
     <row r="96" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G96" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H96" s="16"/>
       <c r="I96" s="11"/>
@@ -9876,14 +9876,14 @@
       <c r="L96" s="11"/>
       <c r="M96" s="11"/>
       <c r="N96" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O96" s="16"/>
       <c r="P96" s="46">
         <v>10.1</v>
       </c>
       <c r="Q96" s="36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R96" s="18"/>
       <c r="S96" s="18"/>
@@ -9892,7 +9892,7 @@
     </row>
     <row r="97" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G97" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H97" s="16"/>
       <c r="I97" s="11"/>
@@ -9901,14 +9901,14 @@
       <c r="L97" s="8"/>
       <c r="M97" s="8"/>
       <c r="N97" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O97" s="16"/>
       <c r="P97" s="46">
         <v>10.199999999999999</v>
       </c>
       <c r="Q97" s="36" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="R97" s="18"/>
       <c r="S97" s="18"/>
@@ -9917,7 +9917,7 @@
     </row>
     <row r="98" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G98" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H98" s="16"/>
       <c r="I98" s="11"/>
@@ -9926,14 +9926,14 @@
       <c r="L98" s="8"/>
       <c r="M98" s="8"/>
       <c r="N98" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O98" s="16"/>
       <c r="P98" s="46">
         <v>10.3</v>
       </c>
       <c r="Q98" s="36" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="R98" s="18"/>
       <c r="S98" s="18"/>
@@ -9942,7 +9942,7 @@
     </row>
     <row r="99" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G99" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H99" s="16"/>
       <c r="I99" s="11"/>
@@ -9951,14 +9951,14 @@
       <c r="L99" s="8"/>
       <c r="M99" s="8"/>
       <c r="N99" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O99" s="16"/>
       <c r="P99" s="46">
         <v>10.4</v>
       </c>
       <c r="Q99" s="36" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="R99" s="18"/>
       <c r="S99" s="18"/>
@@ -9967,7 +9967,7 @@
     </row>
     <row r="100" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G100" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H100" s="16"/>
       <c r="I100" s="11"/>
@@ -9976,14 +9976,14 @@
       <c r="L100" s="8"/>
       <c r="M100" s="8"/>
       <c r="N100" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O100" s="16"/>
       <c r="P100" s="46">
         <v>10.5</v>
       </c>
       <c r="Q100" s="36" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="R100" s="18"/>
       <c r="S100" s="18"/>
@@ -9992,7 +9992,7 @@
     </row>
     <row r="101" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G101" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H101" s="16"/>
       <c r="I101" s="11"/>
@@ -10001,14 +10001,14 @@
       <c r="L101" s="8"/>
       <c r="M101" s="8"/>
       <c r="N101" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O101" s="16"/>
       <c r="U101" s="13"/>
     </row>
     <row r="102" spans="7:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G102" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H102" s="16"/>
       <c r="I102" s="11"/>
@@ -10017,28 +10017,28 @@
       <c r="L102" s="8"/>
       <c r="M102" s="8"/>
       <c r="N102" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O102" s="16"/>
       <c r="P102" s="70">
         <v>11</v>
       </c>
       <c r="Q102" s="67" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="R102" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S102" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S102" s="72" t="s">
+      <c r="T102" s="72" t="s">
         <v>436</v>
-      </c>
-      <c r="T102" s="72" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="103" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G103" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H103" s="16"/>
       <c r="I103" s="11"/>
@@ -10047,14 +10047,14 @@
       <c r="L103" s="8"/>
       <c r="M103" s="8"/>
       <c r="N103" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O103" s="16"/>
       <c r="P103" s="46">
         <v>11.1</v>
       </c>
       <c r="Q103" s="36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R103" s="18"/>
       <c r="S103" s="18"/>
@@ -10063,7 +10063,7 @@
     </row>
     <row r="104" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G104" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H104" s="16"/>
       <c r="I104" s="11"/>
@@ -10077,7 +10077,7 @@
         <v>11.2</v>
       </c>
       <c r="Q104" s="36" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="R104" s="18"/>
       <c r="S104" s="18"/>
@@ -10086,7 +10086,7 @@
     </row>
     <row r="105" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G105" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H105" s="16"/>
       <c r="I105" s="11"/>
@@ -10100,7 +10100,7 @@
         <v>11.3</v>
       </c>
       <c r="Q105" s="36" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="R105" s="18"/>
       <c r="S105" s="18"/>
@@ -10109,7 +10109,7 @@
     </row>
     <row r="106" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G106" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H106" s="16"/>
       <c r="I106" s="11"/>
@@ -10123,7 +10123,7 @@
     </row>
     <row r="107" spans="7:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G107" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H107" s="16"/>
       <c r="I107" s="11"/>
@@ -10137,22 +10137,22 @@
         <v>12</v>
       </c>
       <c r="Q107" s="67" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="R107" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S107" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S107" s="72" t="s">
+      <c r="T107" s="72" t="s">
         <v>436</v>
-      </c>
-      <c r="T107" s="72" t="s">
-        <v>437</v>
       </c>
       <c r="U107" s="16"/>
     </row>
     <row r="108" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G108" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H108" s="16"/>
       <c r="I108" s="11"/>
@@ -10166,7 +10166,7 @@
         <v>12.1</v>
       </c>
       <c r="Q108" s="36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R108" s="18"/>
       <c r="S108" s="18"/>
@@ -10175,7 +10175,7 @@
     </row>
     <row r="109" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G109" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H109" s="16"/>
       <c r="I109" s="11"/>
@@ -10189,7 +10189,7 @@
         <v>12.2</v>
       </c>
       <c r="Q109" s="36" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R109" s="18"/>
       <c r="S109" s="18"/>
@@ -10198,7 +10198,7 @@
     </row>
     <row r="110" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G110" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H110" s="16"/>
       <c r="I110" s="11"/>
@@ -10212,7 +10212,7 @@
         <v>12.3</v>
       </c>
       <c r="Q110" s="36" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="R110" s="18"/>
       <c r="S110" s="18"/>
@@ -10221,7 +10221,7 @@
     </row>
     <row r="111" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G111" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H111" s="16"/>
       <c r="I111" s="11"/>
@@ -10235,7 +10235,7 @@
         <v>12.4</v>
       </c>
       <c r="Q111" s="36" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="R111" s="18"/>
       <c r="S111" s="18"/>
@@ -10244,7 +10244,7 @@
     </row>
     <row r="112" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G112" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H112" s="16"/>
       <c r="I112" s="11"/>
@@ -10258,7 +10258,7 @@
         <v>12.5</v>
       </c>
       <c r="Q112" s="36" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="R112" s="18"/>
       <c r="S112" s="18"/>
@@ -10267,7 +10267,7 @@
     </row>
     <row r="113" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G113" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H113" s="16"/>
       <c r="I113" s="11"/>
@@ -10281,7 +10281,7 @@
         <v>12.6</v>
       </c>
       <c r="Q113" s="36" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="R113" s="18"/>
       <c r="S113" s="18"/>
@@ -10290,7 +10290,7 @@
     </row>
     <row r="114" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G114" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H114" s="16"/>
       <c r="I114" s="11"/>
@@ -10304,7 +10304,7 @@
         <v>12.7</v>
       </c>
       <c r="Q114" s="36" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="R114" s="18"/>
       <c r="S114" s="18"/>
@@ -10313,7 +10313,7 @@
     </row>
     <row r="115" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G115" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H115" s="16"/>
       <c r="I115" s="11"/>
@@ -10327,7 +10327,7 @@
         <v>12.8</v>
       </c>
       <c r="Q115" s="36" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="R115" s="18"/>
       <c r="S115" s="18"/>
@@ -10336,7 +10336,7 @@
     </row>
     <row r="116" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G116" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H116" s="16"/>
       <c r="I116" s="11"/>
@@ -10350,7 +10350,7 @@
         <v>12.9</v>
       </c>
       <c r="Q116" s="36" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="R116" s="18"/>
       <c r="S116" s="18"/>
@@ -10359,7 +10359,7 @@
     </row>
     <row r="117" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G117" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H117" s="16"/>
       <c r="I117" s="11"/>
@@ -10373,7 +10373,7 @@
     </row>
     <row r="118" spans="7:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G118" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H118" s="16"/>
       <c r="I118" s="11"/>
@@ -10387,22 +10387,22 @@
         <v>13</v>
       </c>
       <c r="Q118" s="67" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="R118" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S118" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S118" s="72" t="s">
+      <c r="T118" s="72" t="s">
         <v>436</v>
-      </c>
-      <c r="T118" s="72" t="s">
-        <v>437</v>
       </c>
       <c r="U118" s="13"/>
     </row>
     <row r="119" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G119" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H119" s="16"/>
       <c r="I119" s="11"/>
@@ -10416,7 +10416,7 @@
         <v>13.1</v>
       </c>
       <c r="Q119" s="36" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="R119" s="18"/>
       <c r="S119" s="18"/>
@@ -10425,7 +10425,7 @@
     </row>
     <row r="120" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G120" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H120" s="16"/>
       <c r="I120" s="11"/>
@@ -10439,7 +10439,7 @@
         <v>13.2</v>
       </c>
       <c r="Q120" s="36" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="R120" s="18"/>
       <c r="S120" s="18"/>
@@ -10448,7 +10448,7 @@
     </row>
     <row r="121" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G121" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H121" s="16"/>
       <c r="I121" s="11"/>
@@ -10462,7 +10462,7 @@
         <v>13.3</v>
       </c>
       <c r="Q121" s="36" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R121" s="18"/>
       <c r="S121" s="18"/>
@@ -10471,7 +10471,7 @@
     </row>
     <row r="122" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G122" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H122" s="16"/>
       <c r="I122" s="11"/>
@@ -10485,7 +10485,7 @@
         <v>13.4</v>
       </c>
       <c r="Q122" s="36" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="R122" s="18"/>
       <c r="S122" s="18"/>
@@ -10494,7 +10494,7 @@
     </row>
     <row r="123" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G123" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H123" s="16"/>
       <c r="I123" s="11"/>
@@ -10508,7 +10508,7 @@
         <v>13.5</v>
       </c>
       <c r="Q123" s="36" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="R123" s="18"/>
       <c r="S123" s="18"/>
@@ -10517,7 +10517,7 @@
     </row>
     <row r="124" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G124" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H124" s="16"/>
       <c r="I124" s="11"/>
@@ -10531,7 +10531,7 @@
     </row>
     <row r="125" spans="7:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G125" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H125" s="16"/>
       <c r="I125" s="11"/>
@@ -10545,22 +10545,22 @@
         <v>14</v>
       </c>
       <c r="Q125" s="67" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="R125" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S125" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S125" s="72" t="s">
+      <c r="T125" s="72" t="s">
         <v>436</v>
-      </c>
-      <c r="T125" s="72" t="s">
-        <v>437</v>
       </c>
       <c r="U125" s="16"/>
     </row>
     <row r="126" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G126" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H126" s="16"/>
       <c r="I126" s="11"/>
@@ -10574,7 +10574,7 @@
         <v>14.1</v>
       </c>
       <c r="Q126" s="36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R126" s="18"/>
       <c r="S126" s="18"/>
@@ -10583,7 +10583,7 @@
     </row>
     <row r="127" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G127" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H127" s="16"/>
       <c r="I127" s="11"/>
@@ -10597,7 +10597,7 @@
         <v>14.2</v>
       </c>
       <c r="Q127" s="36" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="R127" s="18"/>
       <c r="S127" s="18"/>
@@ -10606,7 +10606,7 @@
     </row>
     <row r="128" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G128" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H128" s="16"/>
       <c r="I128" s="11"/>
@@ -10620,7 +10620,7 @@
         <v>14.3</v>
       </c>
       <c r="Q128" s="36" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="R128" s="18"/>
       <c r="S128" s="18"/>
@@ -10629,7 +10629,7 @@
     </row>
     <row r="129" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G129" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H129" s="16"/>
       <c r="I129" s="11"/>
@@ -10643,7 +10643,7 @@
         <v>14.4</v>
       </c>
       <c r="Q129" s="36" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="R129" s="18"/>
       <c r="S129" s="18"/>
@@ -10652,7 +10652,7 @@
     </row>
     <row r="130" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G130" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H130" s="16"/>
       <c r="I130" s="11"/>
@@ -10666,7 +10666,7 @@
     </row>
     <row r="131" spans="7:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="G131" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H131" s="16"/>
       <c r="I131" s="11"/>
@@ -10680,22 +10680,22 @@
         <v>15</v>
       </c>
       <c r="Q131" s="67" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R131" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S131" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S131" s="72" t="s">
+      <c r="T131" s="72" t="s">
         <v>436</v>
-      </c>
-      <c r="T131" s="72" t="s">
-        <v>437</v>
       </c>
       <c r="U131" s="16"/>
     </row>
     <row r="132" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G132" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H132" s="16"/>
       <c r="I132" s="11"/>
@@ -10709,7 +10709,7 @@
         <v>15.1</v>
       </c>
       <c r="Q132" s="36" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="R132" s="17"/>
       <c r="S132" s="17"/>
@@ -10718,7 +10718,7 @@
     </row>
     <row r="133" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G133" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H133" s="16"/>
       <c r="I133" s="11"/>
@@ -10732,7 +10732,7 @@
         <v>15.2</v>
       </c>
       <c r="Q133" s="36" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="R133" s="18"/>
       <c r="S133" s="18"/>
@@ -10741,7 +10741,7 @@
     </row>
     <row r="134" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G134" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H134" s="16"/>
       <c r="I134" s="11"/>
@@ -10755,7 +10755,7 @@
         <v>15.3</v>
       </c>
       <c r="Q134" s="36" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R134" s="18"/>
       <c r="S134" s="18"/>
@@ -10764,7 +10764,7 @@
     </row>
     <row r="135" spans="7:21" x14ac:dyDescent="0.35">
       <c r="G135" s="16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H135" s="16"/>
       <c r="I135" s="11"/>
@@ -10778,7 +10778,7 @@
         <v>15.4</v>
       </c>
       <c r="Q135" s="36" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="R135" s="18"/>
       <c r="S135" s="18"/>
@@ -10801,16 +10801,16 @@
         <v>16</v>
       </c>
       <c r="Q137" s="67" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R137" s="71" t="s">
+        <v>434</v>
+      </c>
+      <c r="S137" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="S137" s="72" t="s">
+      <c r="T137" s="72" t="s">
         <v>436</v>
-      </c>
-      <c r="T137" s="72" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="138" spans="7:21" x14ac:dyDescent="0.35">
@@ -10822,7 +10822,7 @@
         <v>16.100000000000001</v>
       </c>
       <c r="Q138" s="36" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="R138" s="18"/>
       <c r="S138" s="18"/>
@@ -10838,7 +10838,7 @@
         <v>16.2</v>
       </c>
       <c r="Q139" s="36" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="R139" s="18"/>
       <c r="S139" s="18"/>
@@ -10854,7 +10854,7 @@
         <v>16.3</v>
       </c>
       <c r="Q140" s="36" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="R140" s="18"/>
       <c r="S140" s="18"/>
@@ -10877,16 +10877,16 @@
         <v>17</v>
       </c>
       <c r="Q142" s="67" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="R142" s="73" t="s">
+        <v>434</v>
+      </c>
+      <c r="S142" s="73" t="s">
         <v>435</v>
       </c>
-      <c r="S142" s="73" t="s">
+      <c r="T142" s="73" t="s">
         <v>436</v>
-      </c>
-      <c r="T142" s="73" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="143" spans="7:21" x14ac:dyDescent="0.35">
@@ -10898,7 +10898,7 @@
         <v>17.100000000000001</v>
       </c>
       <c r="Q143" s="89" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="R143" s="17"/>
       <c r="S143" s="17"/>
@@ -10914,7 +10914,7 @@
         <v>17.2</v>
       </c>
       <c r="Q144" s="36" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="R144" s="18"/>
       <c r="S144" s="18"/>
@@ -10930,7 +10930,7 @@
         <v>17.3</v>
       </c>
       <c r="Q145" s="36" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="R145" s="18"/>
       <c r="S145" s="18"/>
@@ -10946,7 +10946,7 @@
         <v>17.399999999999999</v>
       </c>
       <c r="Q146" s="36" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="R146" s="18"/>
       <c r="S146" s="18"/>
@@ -10962,7 +10962,7 @@
         <v>17.5</v>
       </c>
       <c r="Q147" s="36" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="R147" s="18"/>
       <c r="S147" s="18"/>
@@ -10978,7 +10978,7 @@
         <v>17.600000000000001</v>
       </c>
       <c r="Q148" s="36" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="R148" s="18"/>
       <c r="S148" s="18"/>
@@ -10994,7 +10994,7 @@
         <v>17.7</v>
       </c>
       <c r="Q149" s="36" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="R149" s="18"/>
       <c r="S149" s="18"/>
@@ -11010,7 +11010,7 @@
         <v>17.8</v>
       </c>
       <c r="Q150" s="36" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="R150" s="18"/>
       <c r="S150" s="18"/>
@@ -11026,7 +11026,7 @@
         <v>17.899999999999999</v>
       </c>
       <c r="Q151" s="36" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="R151" s="18"/>
       <c r="S151" s="18"/>
@@ -11049,16 +11049,16 @@
         <v>18</v>
       </c>
       <c r="Q153" s="67" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="R153" s="73" t="s">
+        <v>434</v>
+      </c>
+      <c r="S153" s="73" t="s">
         <v>435</v>
       </c>
-      <c r="S153" s="73" t="s">
+      <c r="T153" s="73" t="s">
         <v>436</v>
-      </c>
-      <c r="T153" s="73" t="s">
-        <v>437</v>
       </c>
       <c r="U153" s="13"/>
     </row>
@@ -11071,7 +11071,7 @@
         <v>18.100000000000001</v>
       </c>
       <c r="Q154" s="89" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="R154" s="34"/>
       <c r="S154" s="17"/>
@@ -11087,7 +11087,7 @@
         <v>18.2</v>
       </c>
       <c r="Q155" s="36" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="R155" s="35"/>
       <c r="S155" s="18"/>
@@ -11103,7 +11103,7 @@
         <v>18.3</v>
       </c>
       <c r="Q156" s="36" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="R156" s="35"/>
       <c r="S156" s="18"/>
@@ -11119,7 +11119,7 @@
         <v>18.399999999999999</v>
       </c>
       <c r="Q157" s="36" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R157" s="35"/>
       <c r="S157" s="18"/>
@@ -11142,16 +11142,16 @@
         <v>19</v>
       </c>
       <c r="Q159" s="67" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="R159" s="73" t="s">
+        <v>434</v>
+      </c>
+      <c r="S159" s="73" t="s">
         <v>435</v>
       </c>
-      <c r="S159" s="73" t="s">
+      <c r="T159" s="73" t="s">
         <v>436</v>
-      </c>
-      <c r="T159" s="73" t="s">
-        <v>437</v>
       </c>
       <c r="U159" s="13"/>
     </row>
@@ -11164,7 +11164,7 @@
         <v>19.100000000000001</v>
       </c>
       <c r="Q160" s="36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R160" s="34"/>
       <c r="S160" s="17"/>
@@ -11180,7 +11180,7 @@
         <v>19.2</v>
       </c>
       <c r="Q161" s="36" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="R161" s="35"/>
       <c r="S161" s="18"/>
@@ -11203,16 +11203,16 @@
         <v>20</v>
       </c>
       <c r="Q163" s="67" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="R163" s="73" t="s">
+        <v>434</v>
+      </c>
+      <c r="S163" s="73" t="s">
         <v>435</v>
       </c>
-      <c r="S163" s="73" t="s">
+      <c r="T163" s="73" t="s">
         <v>436</v>
-      </c>
-      <c r="T163" s="73" t="s">
-        <v>437</v>
       </c>
       <c r="U163" s="13"/>
     </row>
@@ -11225,7 +11225,7 @@
         <v>20.100000000000001</v>
       </c>
       <c r="Q164" s="36" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="R164" s="18"/>
       <c r="S164" s="18"/>
@@ -11241,7 +11241,7 @@
         <v>20.2</v>
       </c>
       <c r="Q165" s="36" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="R165" s="18"/>
       <c r="S165" s="18"/>
